--- a/archives/tours01.xlsx
+++ b/archives/tours01.xlsx
@@ -5,20 +5,16 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cymil\Documents\Dev\tours\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cymil\Documents\Dev\tours\archives\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4D39C7B-4AFF-4A2F-B400-ABB95C4D9468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7F1AB2F-412C-4E49-9D8F-19CDC4639105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DC03C961-6B6A-4A66-B2AD-84658B13F616}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DC03C961-6B6A-4A66-B2AD-84658B13F616}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
-    <sheet name="Feuil3" sheetId="3" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Feuil3!$A$1:$E$242</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -38,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3940" uniqueCount="1092">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2820" uniqueCount="1127">
   <si>
     <t>LEAL</t>
   </si>
@@ -2194,9 +2190,6 @@
     <t>HRYR</t>
   </si>
   <si>
-    <t>HSSJ</t>
-  </si>
-  <si>
     <t>HUEN</t>
   </si>
   <si>
@@ -2212,9 +2205,6 @@
     <t>HHAS</t>
   </si>
   <si>
-    <t>HSSS</t>
-  </si>
-  <si>
     <t>HECA</t>
   </si>
   <si>
@@ -2254,9 +2244,6 @@
     <t>SLLP</t>
   </si>
   <si>
-    <t>SPIM</t>
-  </si>
-  <si>
     <t>SEQU</t>
   </si>
   <si>
@@ -3314,6 +3301,120 @@
   </si>
   <si>
     <t>HSSK</t>
+  </si>
+  <si>
+    <t>HY001</t>
+  </si>
+  <si>
+    <t>Hydravion Canada-USA</t>
+  </si>
+  <si>
+    <t>CAH2</t>
+  </si>
+  <si>
+    <t>CAY4</t>
+  </si>
+  <si>
+    <t>HY002</t>
+  </si>
+  <si>
+    <t>CZSW</t>
+  </si>
+  <si>
+    <t>HY003</t>
+  </si>
+  <si>
+    <t>9C0</t>
+  </si>
+  <si>
+    <t>HY004</t>
+  </si>
+  <si>
+    <t>63A</t>
+  </si>
+  <si>
+    <t>HY005</t>
+  </si>
+  <si>
+    <t>5Z1</t>
+  </si>
+  <si>
+    <t>HY006</t>
+  </si>
+  <si>
+    <t>ZHY01</t>
+  </si>
+  <si>
+    <t>HY007</t>
+  </si>
+  <si>
+    <t>2Y3</t>
+  </si>
+  <si>
+    <t>HY008</t>
+  </si>
+  <si>
+    <t>ZHY02</t>
+  </si>
+  <si>
+    <t>HY009</t>
+  </si>
+  <si>
+    <t>1Z9</t>
+  </si>
+  <si>
+    <t>HY010</t>
+  </si>
+  <si>
+    <t>57AK</t>
+  </si>
+  <si>
+    <t>HY011</t>
+  </si>
+  <si>
+    <t>ZHY03</t>
+  </si>
+  <si>
+    <t>HY012</t>
+  </si>
+  <si>
+    <t>SYB</t>
+  </si>
+  <si>
+    <t>HY013</t>
+  </si>
+  <si>
+    <t>5Z9</t>
+  </si>
+  <si>
+    <t>HY014</t>
+  </si>
+  <si>
+    <t>ZHY04</t>
+  </si>
+  <si>
+    <t>HY015</t>
+  </si>
+  <si>
+    <t>ZHY05</t>
+  </si>
+  <si>
+    <t>HY016</t>
+  </si>
+  <si>
+    <t>AK33</t>
+  </si>
+  <si>
+    <t>HY017</t>
+  </si>
+  <si>
+    <t>ZHY06</t>
+  </si>
+  <si>
+    <t>HY018</t>
+  </si>
+  <si>
+    <t>KQA</t>
   </si>
 </sst>
 </file>
@@ -3671,7 +3772,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10FB3079-391B-4528-AB95-FDAB8E11290D}">
-  <dimension ref="A1:E546"/>
+  <dimension ref="A1:E564"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="44" bestFit="1" customWidth="1"/>
@@ -3682,19 +3783,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D1" t="s">
         <v>1084</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" t="s">
         <v>1085</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1086</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1087</v>
-      </c>
-      <c r="E1" t="s">
-        <v>1088</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -4779,7 +4880,7 @@
         <v>90</v>
       </c>
       <c r="D65" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
       <c r="E65" t="s">
         <v>621</v>
@@ -4793,7 +4894,7 @@
         <v>89</v>
       </c>
       <c r="C66" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
       <c r="D66" t="s">
         <v>91</v>
@@ -8850,7 +8951,7 @@
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="B305" t="s">
         <v>622</v>
@@ -8867,7 +8968,7 @@
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="B306" t="s">
         <v>622</v>
@@ -8884,7 +8985,7 @@
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="B307" t="s">
         <v>622</v>
@@ -8901,7 +9002,7 @@
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="B308" t="s">
         <v>622</v>
@@ -8918,7 +9019,7 @@
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="B309" t="s">
         <v>622</v>
@@ -8935,7 +9036,7 @@
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="B310" t="s">
         <v>622</v>
@@ -8952,7 +9053,7 @@
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="B311" t="s">
         <v>622</v>
@@ -8969,7 +9070,7 @@
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="B312" t="s">
         <v>622</v>
@@ -8986,7 +9087,7 @@
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="B313" t="s">
         <v>622</v>
@@ -9003,7 +9104,7 @@
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="B314" t="s">
         <v>622</v>
@@ -9020,7 +9121,7 @@
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="B315" t="s">
         <v>622</v>
@@ -9037,7 +9138,7 @@
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="B316" t="s">
         <v>622</v>
@@ -9054,7 +9155,7 @@
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="B317" t="s">
         <v>622</v>
@@ -9071,10 +9172,10 @@
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="B318" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C318" t="s">
         <v>635</v>
@@ -9088,10 +9189,10 @@
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="B319" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C319" t="s">
         <v>636</v>
@@ -9105,10 +9206,10 @@
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="B320" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C320" t="s">
         <v>631</v>
@@ -9122,10 +9223,10 @@
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="B321" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C321" t="s">
         <v>637</v>
@@ -9139,10 +9240,10 @@
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="B322" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C322" t="s">
         <v>638</v>
@@ -9156,10 +9257,10 @@
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="B323" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C323" t="s">
         <v>639</v>
@@ -9173,10 +9274,10 @@
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="B324" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C324" t="s">
         <v>293</v>
@@ -9190,10 +9291,10 @@
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="B325" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C325" t="s">
         <v>640</v>
@@ -9207,10 +9308,10 @@
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="B326" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C326" t="s">
         <v>641</v>
@@ -9224,10 +9325,10 @@
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="B327" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C327" t="s">
         <v>642</v>
@@ -9241,10 +9342,10 @@
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="B328" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C328" t="s">
         <v>643</v>
@@ -9258,10 +9359,10 @@
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="B329" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C329" t="s">
         <v>644</v>
@@ -9275,10 +9376,10 @@
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="B330" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C330" t="s">
         <v>645</v>
@@ -9292,10 +9393,10 @@
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="B331" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C331" t="s">
         <v>646</v>
@@ -9309,10 +9410,10 @@
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="B332" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C332" t="s">
         <v>647</v>
@@ -9326,10 +9427,10 @@
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="B333" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C333" t="s">
         <v>648</v>
@@ -9343,10 +9444,10 @@
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="B334" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C334" t="s">
         <v>649</v>
@@ -9360,10 +9461,10 @@
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="B335" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C335" t="s">
         <v>650</v>
@@ -9377,10 +9478,10 @@
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="B336" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C336" t="s">
         <v>651</v>
@@ -9394,10 +9495,10 @@
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="B337" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C337" t="s">
         <v>652</v>
@@ -9411,10 +9512,10 @@
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="B338" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C338" t="s">
         <v>653</v>
@@ -9428,10 +9529,10 @@
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="B339" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C339" t="s">
         <v>654</v>
@@ -9445,10 +9546,10 @@
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="B340" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C340" t="s">
         <v>655</v>
@@ -9462,10 +9563,10 @@
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="B341" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C341" t="s">
         <v>656</v>
@@ -9479,10 +9580,10 @@
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="B342" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C342" t="s">
         <v>657</v>
@@ -9496,10 +9597,10 @@
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="B343" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C343" t="s">
         <v>658</v>
@@ -9513,10 +9614,10 @@
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="B344" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C344" t="s">
         <v>659</v>
@@ -9530,10 +9631,10 @@
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="B345" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C345" t="s">
         <v>660</v>
@@ -9547,10 +9648,10 @@
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="B346" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C346" t="s">
         <v>661</v>
@@ -9564,10 +9665,10 @@
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="B347" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C347" t="s">
         <v>662</v>
@@ -9581,10 +9682,10 @@
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="B348" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C348" t="s">
         <v>663</v>
@@ -9598,10 +9699,10 @@
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="B349" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C349" t="s">
         <v>664</v>
@@ -9615,10 +9716,10 @@
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="B350" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C350" t="s">
         <v>665</v>
@@ -9632,10 +9733,10 @@
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="B351" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C351" t="s">
         <v>666</v>
@@ -9649,10 +9750,10 @@
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="B352" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C352" t="s">
         <v>667</v>
@@ -9666,7 +9767,7 @@
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="B353" t="s">
         <v>669</v>
@@ -9683,7 +9784,7 @@
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="B354" t="s">
         <v>669</v>
@@ -9700,7 +9801,7 @@
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="B355" t="s">
         <v>669</v>
@@ -9717,7 +9818,7 @@
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="B356" t="s">
         <v>669</v>
@@ -9734,7 +9835,7 @@
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="B357" t="s">
         <v>669</v>
@@ -9751,7 +9852,7 @@
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="B358" t="s">
         <v>669</v>
@@ -9768,7 +9869,7 @@
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="B359" t="s">
         <v>669</v>
@@ -9785,7 +9886,7 @@
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="B360" t="s">
         <v>669</v>
@@ -9802,7 +9903,7 @@
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="B361" t="s">
         <v>669</v>
@@ -9819,7 +9920,7 @@
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="B362" t="s">
         <v>669</v>
@@ -9836,7 +9937,7 @@
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="B363" t="s">
         <v>669</v>
@@ -9853,7 +9954,7 @@
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="B364" t="s">
         <v>669</v>
@@ -9870,7 +9971,7 @@
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="B365" t="s">
         <v>669</v>
@@ -9887,7 +9988,7 @@
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="B366" t="s">
         <v>669</v>
@@ -9904,7 +10005,7 @@
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="B367" t="s">
         <v>669</v>
@@ -9921,7 +10022,7 @@
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="B368" t="s">
         <v>669</v>
@@ -9938,7 +10039,7 @@
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="B369" t="s">
         <v>669</v>
@@ -9955,7 +10056,7 @@
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="B370" t="s">
         <v>669</v>
@@ -9972,7 +10073,7 @@
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="B371" t="s">
         <v>669</v>
@@ -9989,7 +10090,7 @@
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="B372" t="s">
         <v>669</v>
@@ -10006,7 +10107,7 @@
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="B373" t="s">
         <v>669</v>
@@ -10023,7 +10124,7 @@
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="B374" t="s">
         <v>669</v>
@@ -10040,7 +10141,7 @@
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="B375" t="s">
         <v>669</v>
@@ -10057,7 +10158,7 @@
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="B376" t="s">
         <v>669</v>
@@ -10074,7 +10175,7 @@
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="B377" t="s">
         <v>694</v>
@@ -10091,7 +10192,7 @@
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="B378" t="s">
         <v>694</v>
@@ -10108,7 +10209,7 @@
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="B379" t="s">
         <v>694</v>
@@ -10125,7 +10226,7 @@
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="B380" t="s">
         <v>694</v>
@@ -10142,7 +10243,7 @@
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
       <c r="B381" t="s">
         <v>694</v>
@@ -10159,7 +10260,7 @@
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="B382" t="s">
         <v>694</v>
@@ -10176,7 +10277,7 @@
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="B383" t="s">
         <v>694</v>
@@ -10193,7 +10294,7 @@
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="B384" t="s">
         <v>694</v>
@@ -10210,7 +10311,7 @@
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="B385" t="s">
         <v>694</v>
@@ -10227,7 +10328,7 @@
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="B386" t="s">
         <v>694</v>
@@ -10244,7 +10345,7 @@
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="B387" t="s">
         <v>694</v>
@@ -10261,7 +10362,7 @@
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="B388" t="s">
         <v>694</v>
@@ -10278,7 +10379,7 @@
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="B389" t="s">
         <v>694</v>
@@ -10295,7 +10396,7 @@
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="B390" t="s">
         <v>694</v>
@@ -10312,7 +10413,7 @@
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B391" t="s">
         <v>694</v>
@@ -10329,7 +10430,7 @@
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="B392" t="s">
         <v>694</v>
@@ -10346,7 +10447,7 @@
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="B393" t="s">
         <v>694</v>
@@ -10363,7 +10464,7 @@
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="B394" t="s">
         <v>694</v>
@@ -10380,7 +10481,7 @@
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="B395" t="s">
         <v>694</v>
@@ -10397,7 +10498,7 @@
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="B396" t="s">
         <v>694</v>
@@ -10414,7 +10515,7 @@
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="B397" t="s">
         <v>694</v>
@@ -10431,7 +10532,7 @@
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="B398" t="s">
         <v>694</v>
@@ -10448,7 +10549,7 @@
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="B399" t="s">
         <v>694</v>
@@ -10465,7 +10566,7 @@
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="B400" t="s">
         <v>694</v>
@@ -10482,7 +10583,7 @@
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="B401" t="s">
         <v>694</v>
@@ -10499,7 +10600,7 @@
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="B402" t="s">
         <v>694</v>
@@ -10516,7 +10617,7 @@
     </row>
     <row r="403" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="B403" t="s">
         <v>694</v>
@@ -10533,7 +10634,7 @@
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="B404" t="s">
         <v>694</v>
@@ -10542,7 +10643,7 @@
         <v>717</v>
       </c>
       <c r="D404" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="E404" t="s">
         <v>624</v>
@@ -10550,16 +10651,16 @@
     </row>
     <row r="405" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="B405" t="s">
         <v>694</v>
       </c>
       <c r="C405" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="D405" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="E405" t="s">
         <v>624</v>
@@ -10567,16 +10668,16 @@
     </row>
     <row r="406" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="B406" t="s">
         <v>694</v>
       </c>
       <c r="C406" t="s">
+        <v>718</v>
+      </c>
+      <c r="D406" t="s">
         <v>719</v>
-      </c>
-      <c r="D406" t="s">
-        <v>720</v>
       </c>
       <c r="E406" t="s">
         <v>624</v>
@@ -10584,16 +10685,16 @@
     </row>
     <row r="407" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="B407" t="s">
         <v>694</v>
       </c>
       <c r="C407" t="s">
+        <v>719</v>
+      </c>
+      <c r="D407" t="s">
         <v>720</v>
-      </c>
-      <c r="D407" t="s">
-        <v>721</v>
       </c>
       <c r="E407" t="s">
         <v>624</v>
@@ -10601,16 +10702,16 @@
     </row>
     <row r="408" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="B408" t="s">
         <v>694</v>
       </c>
       <c r="C408" t="s">
+        <v>720</v>
+      </c>
+      <c r="D408" t="s">
         <v>721</v>
-      </c>
-      <c r="D408" t="s">
-        <v>722</v>
       </c>
       <c r="E408" t="s">
         <v>624</v>
@@ -10618,16 +10719,16 @@
     </row>
     <row r="409" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="B409" t="s">
         <v>694</v>
       </c>
       <c r="C409" t="s">
+        <v>721</v>
+      </c>
+      <c r="D409" t="s">
         <v>722</v>
-      </c>
-      <c r="D409" t="s">
-        <v>723</v>
       </c>
       <c r="E409" t="s">
         <v>624</v>
@@ -10635,16 +10736,16 @@
     </row>
     <row r="410" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="B410" t="s">
         <v>694</v>
       </c>
       <c r="C410" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D410" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
       <c r="E410" t="s">
         <v>624</v>
@@ -10652,16 +10753,16 @@
     </row>
     <row r="411" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="B411" t="s">
         <v>694</v>
       </c>
       <c r="C411" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
       <c r="D411" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="E411" t="s">
         <v>624</v>
@@ -10669,16 +10770,16 @@
     </row>
     <row r="412" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="B412" t="s">
         <v>694</v>
       </c>
       <c r="C412" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D412" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E412" t="s">
         <v>624</v>
@@ -10686,16 +10787,16 @@
     </row>
     <row r="413" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="B413" t="s">
         <v>694</v>
       </c>
       <c r="C413" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="D413" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="E413" t="s">
         <v>624</v>
@@ -10703,13 +10804,13 @@
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="B414" t="s">
         <v>694</v>
       </c>
       <c r="C414" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="D414" t="s">
         <v>8</v>
@@ -10720,7 +10821,7 @@
     </row>
     <row r="415" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="B415" t="s">
         <v>694</v>
@@ -10737,7 +10838,7 @@
     </row>
     <row r="416" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="B416" t="s">
         <v>694</v>
@@ -10754,7 +10855,7 @@
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="B417" t="s">
         <v>694</v>
@@ -10763,7 +10864,7 @@
         <v>274</v>
       </c>
       <c r="D417" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="E417" t="s">
         <v>624</v>
@@ -10771,16 +10872,16 @@
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="B418" t="s">
         <v>694</v>
       </c>
       <c r="C418" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="D418" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="E418" t="s">
         <v>624</v>
@@ -10788,13 +10889,13 @@
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="B419" t="s">
         <v>694</v>
       </c>
       <c r="C419" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="D419" t="s">
         <v>695</v>
@@ -10805,16 +10906,16 @@
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="B420" t="s">
+        <v>728</v>
+      </c>
+      <c r="C420" t="s">
+        <v>729</v>
+      </c>
+      <c r="D420" t="s">
         <v>730</v>
-      </c>
-      <c r="C420" t="s">
-        <v>731</v>
-      </c>
-      <c r="D420" t="s">
-        <v>732</v>
       </c>
       <c r="E420" t="s">
         <v>624</v>
@@ -10822,16 +10923,16 @@
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="B421" t="s">
+        <v>728</v>
+      </c>
+      <c r="C421" t="s">
         <v>730</v>
       </c>
-      <c r="C421" t="s">
-        <v>732</v>
-      </c>
       <c r="D421" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="E421" t="s">
         <v>624</v>
@@ -10839,16 +10940,16 @@
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="B422" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C422" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="D422" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="E422" t="s">
         <v>624</v>
@@ -10856,16 +10957,16 @@
     </row>
     <row r="423" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="B423" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C423" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="D423" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="E423" t="s">
         <v>624</v>
@@ -10873,16 +10974,16 @@
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="B424" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C424" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="D424" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="E424" t="s">
         <v>624</v>
@@ -10890,16 +10991,16 @@
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="B425" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C425" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="D425" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="E425" t="s">
         <v>624</v>
@@ -10907,16 +11008,16 @@
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="B426" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C426" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="D426" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="E426" t="s">
         <v>624</v>
@@ -10924,16 +11025,16 @@
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="B427" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C427" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="D427" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="E427" t="s">
         <v>624</v>
@@ -10941,16 +11042,16 @@
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B428" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C428" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="D428" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="E428" t="s">
         <v>624</v>
@@ -10958,16 +11059,16 @@
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="B429" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C429" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="D429" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="E429" t="s">
         <v>624</v>
@@ -10975,16 +11076,16 @@
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="B430" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C430" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="D430" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="E430" t="s">
         <v>624</v>
@@ -10992,16 +11093,16 @@
     </row>
     <row r="431" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="B431" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C431" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="D431" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="E431" t="s">
         <v>624</v>
@@ -11009,16 +11110,16 @@
     </row>
     <row r="432" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="B432" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C432" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="D432" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="E432" t="s">
         <v>624</v>
@@ -11026,16 +11127,16 @@
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="B433" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C433" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="D433" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="E433" t="s">
         <v>624</v>
@@ -11043,16 +11144,16 @@
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="B434" t="s">
+        <v>742</v>
+      </c>
+      <c r="C434" t="s">
+        <v>744</v>
+      </c>
+      <c r="D434" t="s">
         <v>745</v>
-      </c>
-      <c r="C434" t="s">
-        <v>747</v>
-      </c>
-      <c r="D434" t="s">
-        <v>748</v>
       </c>
       <c r="E434" t="s">
         <v>624</v>
@@ -11060,16 +11161,16 @@
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="B435" t="s">
+        <v>742</v>
+      </c>
+      <c r="C435" t="s">
         <v>745</v>
       </c>
-      <c r="C435" t="s">
-        <v>748</v>
-      </c>
       <c r="D435" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="E435" t="s">
         <v>624</v>
@@ -11077,16 +11178,16 @@
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="B436" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C436" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="D436" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="E436" t="s">
         <v>624</v>
@@ -11094,16 +11195,16 @@
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="B437" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C437" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="D437" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="E437" t="s">
         <v>624</v>
@@ -11111,16 +11212,16 @@
     </row>
     <row r="438" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="B438" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C438" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="D438" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="E438" t="s">
         <v>624</v>
@@ -11128,16 +11229,16 @@
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="B439" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C439" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="D439" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="E439" t="s">
         <v>624</v>
@@ -11145,16 +11246,16 @@
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="B440" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C440" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="D440" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="E440" t="s">
         <v>624</v>
@@ -11162,16 +11263,16 @@
     </row>
     <row r="441" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="B441" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C441" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="D441" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="E441" t="s">
         <v>624</v>
@@ -11179,16 +11280,16 @@
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="B442" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C442" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="D442" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="E442" t="s">
         <v>624</v>
@@ -11196,16 +11297,16 @@
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="B443" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C443" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="D443" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="E443" t="s">
         <v>624</v>
@@ -11213,16 +11314,16 @@
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="B444" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C444" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="D444" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="E444" t="s">
         <v>624</v>
@@ -11230,16 +11331,16 @@
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="B445" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C445" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="D445" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="E445" t="s">
         <v>624</v>
@@ -11247,16 +11348,16 @@
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="B446" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C446" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="D446" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="E446" t="s">
         <v>624</v>
@@ -11264,16 +11365,16 @@
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="B447" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C447" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="D447" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="E447" t="s">
         <v>624</v>
@@ -11281,16 +11382,16 @@
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="B448" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C448" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="D448" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="E448" t="s">
         <v>624</v>
@@ -11298,16 +11399,16 @@
     </row>
     <row r="449" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="B449" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C449" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="D449" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="E449" t="s">
         <v>624</v>
@@ -11315,16 +11416,16 @@
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="B450" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C450" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="D450" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="E450" t="s">
         <v>624</v>
@@ -11332,16 +11433,16 @@
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="B451" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C451" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="D451" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="E451" t="s">
         <v>624</v>
@@ -11349,16 +11450,16 @@
     </row>
     <row r="452" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="B452" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C452" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="D452" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="E452" t="s">
         <v>624</v>
@@ -11366,16 +11467,16 @@
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="B453" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C453" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="D453" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="E453" t="s">
         <v>624</v>
@@ -11383,16 +11484,16 @@
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="B454" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C454" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="D454" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="E454" t="s">
         <v>624</v>
@@ -11400,16 +11501,16 @@
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="B455" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C455" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="D455" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="E455" t="s">
         <v>624</v>
@@ -11417,16 +11518,16 @@
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="B456" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C456" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="D456" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="E456" t="s">
         <v>624</v>
@@ -11434,16 +11535,16 @@
     </row>
     <row r="457" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="B457" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C457" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="D457" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="E457" t="s">
         <v>624</v>
@@ -11451,16 +11552,16 @@
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="B458" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C458" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="D458" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="E458" t="s">
         <v>624</v>
@@ -11468,16 +11569,16 @@
     </row>
     <row r="459" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="B459" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C459" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="D459" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="E459" t="s">
         <v>624</v>
@@ -11485,16 +11586,16 @@
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="B460" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C460" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="D460" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="E460" t="s">
         <v>624</v>
@@ -11502,16 +11603,16 @@
     </row>
     <row r="461" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="B461" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C461" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="D461" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="E461" t="s">
         <v>624</v>
@@ -11519,16 +11620,16 @@
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="B462" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C462" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="D462" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="E462" t="s">
         <v>624</v>
@@ -11536,16 +11637,16 @@
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="B463" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C463" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="D463" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="E463" t="s">
         <v>624</v>
@@ -11553,16 +11654,16 @@
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="B464" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C464" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="D464" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="E464" t="s">
         <v>624</v>
@@ -11570,16 +11671,16 @@
     </row>
     <row r="465" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="B465" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C465" t="s">
         <v>260</v>
       </c>
       <c r="D465" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="E465" t="s">
         <v>624</v>
@@ -11587,16 +11688,16 @@
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="B466" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C466" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="D466" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E466" t="s">
         <v>624</v>
@@ -11604,16 +11705,16 @@
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="B467" t="s">
+        <v>776</v>
+      </c>
+      <c r="C467" t="s">
+        <v>778</v>
+      </c>
+      <c r="D467" t="s">
         <v>779</v>
-      </c>
-      <c r="C467" t="s">
-        <v>781</v>
-      </c>
-      <c r="D467" t="s">
-        <v>782</v>
       </c>
       <c r="E467" t="s">
         <v>624</v>
@@ -11621,50 +11722,50 @@
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="B468" t="s">
+        <v>776</v>
+      </c>
+      <c r="C468" t="s">
         <v>779</v>
       </c>
-      <c r="C468" t="s">
-        <v>782</v>
-      </c>
       <c r="D468" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="E468" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
     </row>
     <row r="469" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="B469" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C469" t="s">
+        <v>780</v>
+      </c>
+      <c r="D469" t="s">
+        <v>782</v>
+      </c>
+      <c r="E469" t="s">
         <v>783</v>
-      </c>
-      <c r="D469" t="s">
-        <v>785</v>
-      </c>
-      <c r="E469" t="s">
-        <v>786</v>
       </c>
     </row>
     <row r="470" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="B470" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C470" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="D470" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="E470" t="s">
         <v>624</v>
@@ -11672,16 +11773,16 @@
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="B471" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C471" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="D471" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="E471" t="s">
         <v>624</v>
@@ -11689,16 +11790,16 @@
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="B472" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C472" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="D472" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="E472" t="s">
         <v>624</v>
@@ -11706,44 +11807,44 @@
     </row>
     <row r="473" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="B473" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C473" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="D473" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="E473" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
     </row>
     <row r="474" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="B474" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C474" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="D474" t="s">
         <v>31</v>
       </c>
       <c r="E474" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
     </row>
     <row r="475" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="B475" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C475" t="s">
         <v>31</v>
@@ -11757,16 +11858,16 @@
     </row>
     <row r="476" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="B476" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C476" t="s">
         <v>232</v>
       </c>
       <c r="D476" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="E476" t="s">
         <v>624</v>
@@ -11774,16 +11875,16 @@
     </row>
     <row r="477" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="B477" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C477" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="D477" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="E477" t="s">
         <v>624</v>
@@ -11791,16 +11892,16 @@
     </row>
     <row r="478" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="B478" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C478" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="D478" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="E478" t="s">
         <v>624</v>
@@ -11808,44 +11909,44 @@
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="B479" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C479" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="D479" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="E479" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
     </row>
     <row r="480" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="B480" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C480" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="D480" t="s">
         <v>28</v>
       </c>
       <c r="E480" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
     </row>
     <row r="481" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="B481" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C481" t="s">
         <v>28</v>
@@ -11859,16 +11960,16 @@
     </row>
     <row r="482" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="B482" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C482" t="s">
         <v>634</v>
       </c>
       <c r="D482" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="E482" t="s">
         <v>624</v>
@@ -11876,16 +11977,16 @@
     </row>
     <row r="483" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="B483" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C483" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="D483" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="E483" t="s">
         <v>624</v>
@@ -11893,16 +11994,16 @@
     </row>
     <row r="484" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="B484" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C484" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="D484" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="E484" t="s">
         <v>624</v>
@@ -11910,50 +12011,50 @@
     </row>
     <row r="485" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="B485" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C485" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="D485" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="E485" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
     </row>
     <row r="486" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="B486" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C486" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="D486" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="E486" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
     </row>
     <row r="487" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="B487" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C487" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="D487" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="E487" t="s">
         <v>624</v>
@@ -11961,16 +12062,16 @@
     </row>
     <row r="488" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="B488" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C488" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="D488" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="E488" t="s">
         <v>624</v>
@@ -11978,13 +12079,13 @@
     </row>
     <row r="489" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="B489" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C489" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="D489" t="s">
         <v>262</v>
@@ -11995,13 +12096,13 @@
     </row>
     <row r="490" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="B490" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="C490" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="D490" t="s">
         <v>273</v>
@@ -12012,16 +12113,16 @@
     </row>
     <row r="491" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="B491" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="C491" t="s">
         <v>273</v>
       </c>
       <c r="D491" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="E491" t="s">
         <v>624</v>
@@ -12029,13 +12130,13 @@
     </row>
     <row r="492" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="B492" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="C492" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="D492" t="s">
         <v>11</v>
@@ -12046,16 +12147,16 @@
     </row>
     <row r="493" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="B493" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="C493" t="s">
         <v>11</v>
       </c>
       <c r="D493" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E493" t="s">
         <v>624</v>
@@ -12063,16 +12164,16 @@
     </row>
     <row r="494" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="B494" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="C494" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D494" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="E494" t="s">
         <v>624</v>
@@ -12080,13 +12181,13 @@
     </row>
     <row r="495" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="B495" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="C495" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="D495" t="s">
         <v>300</v>
@@ -12097,10 +12198,10 @@
     </row>
     <row r="496" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="B496" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="C496" t="s">
         <v>300</v>
@@ -12114,16 +12215,16 @@
     </row>
     <row r="497" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="B497" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="C497" t="s">
         <v>303</v>
       </c>
       <c r="D497" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="E497" t="s">
         <v>624</v>
@@ -12131,16 +12232,16 @@
     </row>
     <row r="498" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="B498" t="s">
+        <v>799</v>
+      </c>
+      <c r="C498" t="s">
         <v>802</v>
       </c>
-      <c r="C498" t="s">
-        <v>805</v>
-      </c>
       <c r="D498" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="E498" t="s">
         <v>624</v>
@@ -12148,16 +12249,16 @@
     </row>
     <row r="499" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="B499" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="C499" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="D499" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="E499" t="s">
         <v>624</v>
@@ -12165,16 +12266,16 @@
     </row>
     <row r="500" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
       <c r="B500" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="C500" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="D500" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="E500" t="s">
         <v>624</v>
@@ -12182,16 +12283,16 @@
     </row>
     <row r="501" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>1038</v>
+        <v>1035</v>
       </c>
       <c r="B501" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="C501" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="D501" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="E501" t="s">
         <v>624</v>
@@ -12199,16 +12300,16 @@
     </row>
     <row r="502" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="B502" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="C502" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="D502" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="E502" t="s">
         <v>624</v>
@@ -12216,16 +12317,16 @@
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="B503" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="C503" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="D503" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="E503" t="s">
         <v>624</v>
@@ -12233,16 +12334,16 @@
     </row>
     <row r="504" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="B504" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="C504" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="D504" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="E504" t="s">
         <v>624</v>
@@ -12250,16 +12351,16 @@
     </row>
     <row r="505" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="B505" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="C505" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="D505" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="E505" t="s">
         <v>624</v>
@@ -12267,16 +12368,16 @@
     </row>
     <row r="506" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="B506" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="C506" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="D506" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="E506" t="s">
         <v>624</v>
@@ -12284,16 +12385,16 @@
     </row>
     <row r="507" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="B507" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="C507" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="D507" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="E507" t="s">
         <v>624</v>
@@ -12301,16 +12402,16 @@
     </row>
     <row r="508" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="B508" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="C508" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="D508" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="E508" t="s">
         <v>624</v>
@@ -12318,16 +12419,16 @@
     </row>
     <row r="509" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="B509" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="C509" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="D509" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="E509" t="s">
         <v>624</v>
@@ -12335,13 +12436,13 @@
     </row>
     <row r="510" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="B510" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="C510" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="D510" t="s">
         <v>682</v>
@@ -12352,16 +12453,16 @@
     </row>
     <row r="511" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="B511" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="C511" t="s">
         <v>682</v>
       </c>
       <c r="D511" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="E511" t="s">
         <v>624</v>
@@ -12369,16 +12470,16 @@
     </row>
     <row r="512" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="B512" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="C512" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="D512" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="E512" t="s">
         <v>624</v>
@@ -12386,16 +12487,16 @@
     </row>
     <row r="513" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="B513" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="C513" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="D513" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="E513" t="s">
         <v>624</v>
@@ -12403,13 +12504,13 @@
     </row>
     <row r="514" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="B514" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C514" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="D514" t="s">
         <v>630</v>
@@ -12420,16 +12521,16 @@
     </row>
     <row r="515" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="B515" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C515" t="s">
         <v>630</v>
       </c>
       <c r="D515" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="E515" t="s">
         <v>624</v>
@@ -12437,16 +12538,16 @@
     </row>
     <row r="516" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="B516" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C516" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="D516" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="E516" t="s">
         <v>624</v>
@@ -12454,16 +12555,16 @@
     </row>
     <row r="517" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="B517" t="s">
+        <v>816</v>
+      </c>
+      <c r="C517" t="s">
+        <v>818</v>
+      </c>
+      <c r="D517" t="s">
         <v>819</v>
-      </c>
-      <c r="C517" t="s">
-        <v>821</v>
-      </c>
-      <c r="D517" t="s">
-        <v>822</v>
       </c>
       <c r="E517" t="s">
         <v>624</v>
@@ -12471,13 +12572,13 @@
     </row>
     <row r="518" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="B518" t="s">
+        <v>816</v>
+      </c>
+      <c r="C518" t="s">
         <v>819</v>
-      </c>
-      <c r="C518" t="s">
-        <v>822</v>
       </c>
       <c r="D518" t="s">
         <v>270</v>
@@ -12488,16 +12589,16 @@
     </row>
     <row r="519" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="B519" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C519" t="s">
         <v>270</v>
       </c>
       <c r="D519" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="E519" t="s">
         <v>624</v>
@@ -12505,13 +12606,13 @@
     </row>
     <row r="520" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="B520" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C520" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="D520" t="s">
         <v>8</v>
@@ -12522,16 +12623,16 @@
     </row>
     <row r="521" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="B521" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C521" t="s">
         <v>8</v>
       </c>
       <c r="D521" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="E521" t="s">
         <v>624</v>
@@ -12539,16 +12640,16 @@
     </row>
     <row r="522" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="B522" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C522" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="D522" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="E522" t="s">
         <v>624</v>
@@ -12556,16 +12657,16 @@
     </row>
     <row r="523" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="B523" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C523" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="D523" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="E523" t="s">
         <v>624</v>
@@ -12573,16 +12674,16 @@
     </row>
     <row r="524" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="B524" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C524" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="D524" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="E524" t="s">
         <v>624</v>
@@ -12590,16 +12691,16 @@
     </row>
     <row r="525" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="B525" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C525" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="D525" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E525" t="s">
         <v>624</v>
@@ -12607,16 +12708,16 @@
     </row>
     <row r="526" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="B526" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C526" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="D526" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="E526" t="s">
         <v>624</v>
@@ -12624,16 +12725,16 @@
     </row>
     <row r="527" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="B527" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C527" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="D527" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="E527" t="s">
         <v>624</v>
@@ -12641,16 +12742,16 @@
     </row>
     <row r="528" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="B528" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C528" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="D528" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="E528" t="s">
         <v>624</v>
@@ -12658,16 +12759,16 @@
     </row>
     <row r="529" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="B529" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C529" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="D529" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="E529" t="s">
         <v>624</v>
@@ -12675,16 +12776,16 @@
     </row>
     <row r="530" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="B530" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C530" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="D530" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="E530" t="s">
         <v>624</v>
@@ -12692,16 +12793,16 @@
     </row>
     <row r="531" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="B531" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C531" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="D531" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="E531" t="s">
         <v>624</v>
@@ -12709,16 +12810,16 @@
     </row>
     <row r="532" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="B532" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C532" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="D532" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="E532" t="s">
         <v>624</v>
@@ -12726,16 +12827,16 @@
     </row>
     <row r="533" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="B533" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C533" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="D533" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="E533" t="s">
         <v>624</v>
@@ -12743,16 +12844,16 @@
     </row>
     <row r="534" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="B534" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C534" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="D534" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="E534" t="s">
         <v>624</v>
@@ -12760,16 +12861,16 @@
     </row>
     <row r="535" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="B535" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C535" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="D535" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="E535" t="s">
         <v>624</v>
@@ -12777,13 +12878,13 @@
     </row>
     <row r="536" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="B536" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C536" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="D536" t="s">
         <v>293</v>
@@ -12794,10 +12895,10 @@
     </row>
     <row r="537" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="B537" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C537" t="s">
         <v>293</v>
@@ -12811,16 +12912,16 @@
     </row>
     <row r="538" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
       <c r="B538" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C538" t="s">
         <v>149</v>
       </c>
       <c r="D538" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="E538" t="s">
         <v>624</v>
@@ -12828,16 +12929,16 @@
     </row>
     <row r="539" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="B539" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C539" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="D539" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="E539" t="s">
         <v>624</v>
@@ -12845,16 +12946,16 @@
     </row>
     <row r="540" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
       <c r="B540" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C540" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="D540" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="E540" t="s">
         <v>624</v>
@@ -12862,13 +12963,13 @@
     </row>
     <row r="541" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="B541" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C541" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="D541" t="s">
         <v>58</v>
@@ -12879,16 +12980,16 @@
     </row>
     <row r="542" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="B542" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C542" t="s">
         <v>58</v>
       </c>
       <c r="D542" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="E542" t="s">
         <v>624</v>
@@ -12896,13 +12997,13 @@
     </row>
     <row r="543" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="B543" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C543" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="D543" t="s">
         <v>292</v>
@@ -12913,10 +13014,10 @@
     </row>
     <row r="544" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="B544" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C544" t="s">
         <v>292</v>
@@ -12930,10 +13031,10 @@
     </row>
     <row r="545" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="B545" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C545" t="s">
         <v>71</v>
@@ -12947,4151 +13048,325 @@
     </row>
     <row r="546" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="B546" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C546" t="s">
         <v>260</v>
       </c>
       <c r="D546" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="E546" t="s">
         <v>624</v>
       </c>
     </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C8FCFDC-64AF-4CCD-A130-6FF3115558A8}">
-  <dimension ref="A1:E242"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.7109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>841</v>
-      </c>
-      <c r="B1" t="s">
-        <v>622</v>
-      </c>
-      <c r="C1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" t="s">
-        <v>623</v>
-      </c>
-      <c r="E1" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>842</v>
-      </c>
-      <c r="B2" t="s">
-        <v>622</v>
-      </c>
-      <c r="C2" t="s">
-        <v>623</v>
-      </c>
-      <c r="D2" t="s">
-        <v>625</v>
-      </c>
-      <c r="E2" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>843</v>
-      </c>
-      <c r="B3" t="s">
-        <v>622</v>
-      </c>
-      <c r="C3" t="s">
-        <v>625</v>
-      </c>
-      <c r="D3" t="s">
-        <v>626</v>
-      </c>
-      <c r="E3" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>844</v>
-      </c>
-      <c r="B4" t="s">
-        <v>622</v>
-      </c>
-      <c r="C4" t="s">
-        <v>626</v>
-      </c>
-      <c r="D4" t="s">
-        <v>260</v>
-      </c>
-      <c r="E4" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>845</v>
-      </c>
-      <c r="B5" t="s">
-        <v>622</v>
-      </c>
-      <c r="C5" t="s">
-        <v>260</v>
-      </c>
-      <c r="D5" t="s">
-        <v>627</v>
-      </c>
-      <c r="E5" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>846</v>
-      </c>
-      <c r="B6" t="s">
-        <v>622</v>
-      </c>
-      <c r="C6" t="s">
-        <v>627</v>
-      </c>
-      <c r="D6" t="s">
-        <v>628</v>
-      </c>
-      <c r="E6" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>847</v>
-      </c>
-      <c r="B7" t="s">
-        <v>622</v>
-      </c>
-      <c r="C7" t="s">
-        <v>628</v>
-      </c>
-      <c r="D7" t="s">
-        <v>629</v>
-      </c>
-      <c r="E7" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>848</v>
-      </c>
-      <c r="B8" t="s">
-        <v>622</v>
-      </c>
-      <c r="C8" t="s">
-        <v>629</v>
-      </c>
-      <c r="D8" t="s">
-        <v>630</v>
-      </c>
-      <c r="E8" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>849</v>
-      </c>
-      <c r="B9" t="s">
-        <v>622</v>
-      </c>
-      <c r="C9" t="s">
-        <v>630</v>
-      </c>
-      <c r="D9" t="s">
-        <v>631</v>
-      </c>
-      <c r="E9" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>850</v>
-      </c>
-      <c r="B10" t="s">
-        <v>622</v>
-      </c>
-      <c r="C10" t="s">
-        <v>631</v>
-      </c>
-      <c r="D10" t="s">
-        <v>632</v>
-      </c>
-      <c r="E10" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>851</v>
-      </c>
-      <c r="B11" t="s">
-        <v>622</v>
-      </c>
-      <c r="C11" t="s">
-        <v>632</v>
-      </c>
-      <c r="D11" t="s">
-        <v>633</v>
-      </c>
-      <c r="E11" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>852</v>
-      </c>
-      <c r="B12" t="s">
-        <v>622</v>
-      </c>
-      <c r="C12" t="s">
-        <v>633</v>
-      </c>
-      <c r="D12" t="s">
-        <v>634</v>
-      </c>
-      <c r="E12" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>853</v>
-      </c>
-      <c r="B13" t="s">
-        <v>622</v>
-      </c>
-      <c r="C13" t="s">
-        <v>634</v>
-      </c>
-      <c r="D13" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>855</v>
-      </c>
-      <c r="B14" t="s">
-        <v>854</v>
-      </c>
-      <c r="C14" t="s">
-        <v>635</v>
-      </c>
-      <c r="D14" t="s">
-        <v>636</v>
-      </c>
-      <c r="E14" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>856</v>
-      </c>
-      <c r="B15" t="s">
-        <v>854</v>
-      </c>
-      <c r="C15" t="s">
-        <v>636</v>
-      </c>
-      <c r="D15" t="s">
-        <v>631</v>
-      </c>
-      <c r="E15" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>857</v>
-      </c>
-      <c r="B16" t="s">
-        <v>854</v>
-      </c>
-      <c r="C16" t="s">
-        <v>631</v>
-      </c>
-      <c r="D16" t="s">
-        <v>637</v>
-      </c>
-      <c r="E16" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>858</v>
-      </c>
-      <c r="B17" t="s">
-        <v>854</v>
-      </c>
-      <c r="C17" t="s">
-        <v>637</v>
-      </c>
-      <c r="D17" t="s">
-        <v>638</v>
-      </c>
-      <c r="E17" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>859</v>
-      </c>
-      <c r="B18" t="s">
-        <v>854</v>
-      </c>
-      <c r="C18" t="s">
-        <v>638</v>
-      </c>
-      <c r="D18" t="s">
-        <v>639</v>
-      </c>
-      <c r="E18" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>860</v>
-      </c>
-      <c r="B19" t="s">
-        <v>854</v>
-      </c>
-      <c r="C19" t="s">
-        <v>639</v>
-      </c>
-      <c r="D19" t="s">
-        <v>293</v>
-      </c>
-      <c r="E19" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>861</v>
-      </c>
-      <c r="B20" t="s">
-        <v>854</v>
-      </c>
-      <c r="C20" t="s">
-        <v>293</v>
-      </c>
-      <c r="D20" t="s">
-        <v>640</v>
-      </c>
-      <c r="E20" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>862</v>
-      </c>
-      <c r="B21" t="s">
-        <v>854</v>
-      </c>
-      <c r="C21" t="s">
-        <v>640</v>
-      </c>
-      <c r="D21" t="s">
-        <v>641</v>
-      </c>
-      <c r="E21" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>863</v>
-      </c>
-      <c r="B22" t="s">
-        <v>854</v>
-      </c>
-      <c r="C22" t="s">
-        <v>641</v>
-      </c>
-      <c r="D22" t="s">
-        <v>642</v>
-      </c>
-      <c r="E22" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>864</v>
-      </c>
-      <c r="B23" t="s">
-        <v>854</v>
-      </c>
-      <c r="C23" t="s">
-        <v>642</v>
-      </c>
-      <c r="D23" t="s">
-        <v>643</v>
-      </c>
-      <c r="E23" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>865</v>
-      </c>
-      <c r="B24" t="s">
-        <v>854</v>
-      </c>
-      <c r="C24" t="s">
-        <v>643</v>
-      </c>
-      <c r="D24" t="s">
-        <v>644</v>
-      </c>
-      <c r="E24" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>866</v>
-      </c>
-      <c r="B25" t="s">
-        <v>854</v>
-      </c>
-      <c r="C25" t="s">
-        <v>644</v>
-      </c>
-      <c r="D25" t="s">
-        <v>645</v>
-      </c>
-      <c r="E25" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>867</v>
-      </c>
-      <c r="B26" t="s">
-        <v>854</v>
-      </c>
-      <c r="C26" t="s">
-        <v>645</v>
-      </c>
-      <c r="D26" t="s">
-        <v>646</v>
-      </c>
-      <c r="E26" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>868</v>
-      </c>
-      <c r="B27" t="s">
-        <v>854</v>
-      </c>
-      <c r="C27" t="s">
-        <v>646</v>
-      </c>
-      <c r="D27" t="s">
-        <v>647</v>
-      </c>
-      <c r="E27" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>869</v>
-      </c>
-      <c r="B28" t="s">
-        <v>854</v>
-      </c>
-      <c r="C28" t="s">
-        <v>647</v>
-      </c>
-      <c r="D28" t="s">
-        <v>648</v>
-      </c>
-      <c r="E28" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>870</v>
-      </c>
-      <c r="B29" t="s">
-        <v>854</v>
-      </c>
-      <c r="C29" t="s">
-        <v>648</v>
-      </c>
-      <c r="D29" t="s">
-        <v>649</v>
-      </c>
-      <c r="E29" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>871</v>
-      </c>
-      <c r="B30" t="s">
-        <v>854</v>
-      </c>
-      <c r="C30" t="s">
-        <v>649</v>
-      </c>
-      <c r="D30" t="s">
-        <v>650</v>
-      </c>
-      <c r="E30" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>872</v>
-      </c>
-      <c r="B31" t="s">
-        <v>854</v>
-      </c>
-      <c r="C31" t="s">
-        <v>650</v>
-      </c>
-      <c r="D31" t="s">
-        <v>651</v>
-      </c>
-      <c r="E31" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>873</v>
-      </c>
-      <c r="B32" t="s">
-        <v>854</v>
-      </c>
-      <c r="C32" t="s">
-        <v>651</v>
-      </c>
-      <c r="D32" t="s">
-        <v>652</v>
-      </c>
-      <c r="E32" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>874</v>
-      </c>
-      <c r="B33" t="s">
-        <v>854</v>
-      </c>
-      <c r="C33" t="s">
-        <v>652</v>
-      </c>
-      <c r="D33" t="s">
-        <v>653</v>
-      </c>
-      <c r="E33" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>875</v>
-      </c>
-      <c r="B34" t="s">
-        <v>854</v>
-      </c>
-      <c r="C34" t="s">
-        <v>653</v>
-      </c>
-      <c r="D34" t="s">
-        <v>654</v>
-      </c>
-      <c r="E34" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>876</v>
-      </c>
-      <c r="B35" t="s">
-        <v>854</v>
-      </c>
-      <c r="C35" t="s">
-        <v>654</v>
-      </c>
-      <c r="D35" t="s">
-        <v>655</v>
-      </c>
-      <c r="E35" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>877</v>
-      </c>
-      <c r="B36" t="s">
-        <v>854</v>
-      </c>
-      <c r="C36" t="s">
-        <v>655</v>
-      </c>
-      <c r="D36" t="s">
-        <v>656</v>
-      </c>
-      <c r="E36" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>878</v>
-      </c>
-      <c r="B37" t="s">
-        <v>854</v>
-      </c>
-      <c r="C37" t="s">
-        <v>656</v>
-      </c>
-      <c r="D37" t="s">
-        <v>657</v>
-      </c>
-      <c r="E37" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>879</v>
-      </c>
-      <c r="B38" t="s">
-        <v>854</v>
-      </c>
-      <c r="C38" t="s">
-        <v>657</v>
-      </c>
-      <c r="D38" t="s">
-        <v>658</v>
-      </c>
-      <c r="E38" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>880</v>
-      </c>
-      <c r="B39" t="s">
-        <v>854</v>
-      </c>
-      <c r="C39" t="s">
-        <v>658</v>
-      </c>
-      <c r="D39" t="s">
-        <v>659</v>
-      </c>
-      <c r="E39" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>881</v>
-      </c>
-      <c r="B40" t="s">
-        <v>854</v>
-      </c>
-      <c r="C40" t="s">
-        <v>659</v>
-      </c>
-      <c r="D40" t="s">
-        <v>660</v>
-      </c>
-      <c r="E40" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>882</v>
-      </c>
-      <c r="B41" t="s">
-        <v>854</v>
-      </c>
-      <c r="C41" t="s">
-        <v>660</v>
-      </c>
-      <c r="D41" t="s">
-        <v>661</v>
-      </c>
-      <c r="E41" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>883</v>
-      </c>
-      <c r="B42" t="s">
-        <v>854</v>
-      </c>
-      <c r="C42" t="s">
-        <v>661</v>
-      </c>
-      <c r="D42" t="s">
-        <v>662</v>
-      </c>
-      <c r="E42" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>884</v>
-      </c>
-      <c r="B43" t="s">
-        <v>854</v>
-      </c>
-      <c r="C43" t="s">
-        <v>662</v>
-      </c>
-      <c r="D43" t="s">
-        <v>663</v>
-      </c>
-      <c r="E43" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>885</v>
-      </c>
-      <c r="B44" t="s">
-        <v>854</v>
-      </c>
-      <c r="C44" t="s">
-        <v>663</v>
-      </c>
-      <c r="D44" t="s">
-        <v>664</v>
-      </c>
-      <c r="E44" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>886</v>
-      </c>
-      <c r="B45" t="s">
-        <v>854</v>
-      </c>
-      <c r="C45" t="s">
-        <v>664</v>
-      </c>
-      <c r="D45" t="s">
-        <v>665</v>
-      </c>
-      <c r="E45" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>887</v>
-      </c>
-      <c r="B46" t="s">
-        <v>854</v>
-      </c>
-      <c r="C46" t="s">
-        <v>665</v>
-      </c>
-      <c r="D46" t="s">
-        <v>666</v>
-      </c>
-      <c r="E46" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>888</v>
-      </c>
-      <c r="B47" t="s">
-        <v>854</v>
-      </c>
-      <c r="C47" t="s">
-        <v>666</v>
-      </c>
-      <c r="D47" t="s">
-        <v>667</v>
-      </c>
-      <c r="E47" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>889</v>
-      </c>
-      <c r="B48" t="s">
-        <v>854</v>
-      </c>
-      <c r="C48" t="s">
-        <v>667</v>
-      </c>
-      <c r="D48" t="s">
-        <v>668</v>
-      </c>
-      <c r="E48" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>890</v>
-      </c>
-      <c r="B49" t="s">
-        <v>669</v>
-      </c>
-      <c r="C49" t="s">
-        <v>670</v>
-      </c>
-      <c r="D49" t="s">
-        <v>671</v>
-      </c>
-      <c r="E49" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>891</v>
-      </c>
-      <c r="B50" t="s">
-        <v>669</v>
-      </c>
-      <c r="C50" t="s">
-        <v>671</v>
-      </c>
-      <c r="D50" t="s">
-        <v>672</v>
-      </c>
-      <c r="E50" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>892</v>
-      </c>
-      <c r="B51" t="s">
-        <v>669</v>
-      </c>
-      <c r="C51" t="s">
-        <v>672</v>
-      </c>
-      <c r="D51" t="s">
-        <v>673</v>
-      </c>
-      <c r="E51" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>893</v>
-      </c>
-      <c r="B52" t="s">
-        <v>669</v>
-      </c>
-      <c r="C52" t="s">
-        <v>673</v>
-      </c>
-      <c r="D52" t="s">
-        <v>674</v>
-      </c>
-      <c r="E52" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>894</v>
-      </c>
-      <c r="B53" t="s">
-        <v>669</v>
-      </c>
-      <c r="C53" t="s">
-        <v>674</v>
-      </c>
-      <c r="D53" t="s">
-        <v>675</v>
-      </c>
-      <c r="E53" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>895</v>
-      </c>
-      <c r="B54" t="s">
-        <v>669</v>
-      </c>
-      <c r="C54" t="s">
-        <v>675</v>
-      </c>
-      <c r="D54" t="s">
-        <v>676</v>
-      </c>
-      <c r="E54" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>896</v>
-      </c>
-      <c r="B55" t="s">
-        <v>669</v>
-      </c>
-      <c r="C55" t="s">
-        <v>676</v>
-      </c>
-      <c r="D55" t="s">
-        <v>677</v>
-      </c>
-      <c r="E55" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>897</v>
-      </c>
-      <c r="B56" t="s">
-        <v>669</v>
-      </c>
-      <c r="C56" t="s">
-        <v>677</v>
-      </c>
-      <c r="D56" t="s">
-        <v>678</v>
-      </c>
-      <c r="E56" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>898</v>
-      </c>
-      <c r="B57" t="s">
-        <v>669</v>
-      </c>
-      <c r="C57" t="s">
-        <v>678</v>
-      </c>
-      <c r="D57" t="s">
-        <v>679</v>
-      </c>
-      <c r="E57" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>899</v>
-      </c>
-      <c r="B58" t="s">
-        <v>669</v>
-      </c>
-      <c r="C58" t="s">
-        <v>679</v>
-      </c>
-      <c r="D58" t="s">
-        <v>680</v>
-      </c>
-      <c r="E58" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>900</v>
-      </c>
-      <c r="B59" t="s">
-        <v>669</v>
-      </c>
-      <c r="C59" t="s">
-        <v>680</v>
-      </c>
-      <c r="D59" t="s">
-        <v>681</v>
-      </c>
-      <c r="E59" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>901</v>
-      </c>
-      <c r="B60" t="s">
-        <v>669</v>
-      </c>
-      <c r="C60" t="s">
-        <v>681</v>
-      </c>
-      <c r="D60" t="s">
-        <v>682</v>
-      </c>
-      <c r="E60" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>902</v>
-      </c>
-      <c r="B61" t="s">
-        <v>669</v>
-      </c>
-      <c r="C61" t="s">
-        <v>682</v>
-      </c>
-      <c r="D61" t="s">
-        <v>683</v>
-      </c>
-      <c r="E61" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>903</v>
-      </c>
-      <c r="B62" t="s">
-        <v>669</v>
-      </c>
-      <c r="C62" t="s">
-        <v>683</v>
-      </c>
-      <c r="D62" t="s">
-        <v>684</v>
-      </c>
-      <c r="E62" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>904</v>
-      </c>
-      <c r="B63" t="s">
-        <v>669</v>
-      </c>
-      <c r="C63" t="s">
-        <v>684</v>
-      </c>
-      <c r="D63" t="s">
-        <v>685</v>
-      </c>
-      <c r="E63" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>905</v>
-      </c>
-      <c r="B64" t="s">
-        <v>669</v>
-      </c>
-      <c r="C64" t="s">
-        <v>685</v>
-      </c>
-      <c r="D64" t="s">
-        <v>686</v>
-      </c>
-      <c r="E64" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>906</v>
-      </c>
-      <c r="B65" t="s">
-        <v>669</v>
-      </c>
-      <c r="C65" t="s">
-        <v>686</v>
-      </c>
-      <c r="D65" t="s">
-        <v>687</v>
-      </c>
-      <c r="E65" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>907</v>
-      </c>
-      <c r="B66" t="s">
-        <v>669</v>
-      </c>
-      <c r="C66" t="s">
-        <v>687</v>
-      </c>
-      <c r="D66" t="s">
-        <v>688</v>
-      </c>
-      <c r="E66" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>908</v>
-      </c>
-      <c r="B67" t="s">
-        <v>669</v>
-      </c>
-      <c r="C67" t="s">
-        <v>688</v>
-      </c>
-      <c r="D67" t="s">
-        <v>689</v>
-      </c>
-      <c r="E67" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>909</v>
-      </c>
-      <c r="B68" t="s">
-        <v>669</v>
-      </c>
-      <c r="C68" t="s">
-        <v>689</v>
-      </c>
-      <c r="D68" t="s">
-        <v>690</v>
-      </c>
-      <c r="E68" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>910</v>
-      </c>
-      <c r="B69" t="s">
-        <v>669</v>
-      </c>
-      <c r="C69" t="s">
-        <v>690</v>
-      </c>
-      <c r="D69" t="s">
-        <v>691</v>
-      </c>
-      <c r="E69" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>911</v>
-      </c>
-      <c r="B70" t="s">
-        <v>669</v>
-      </c>
-      <c r="C70" t="s">
-        <v>691</v>
-      </c>
-      <c r="D70" t="s">
-        <v>692</v>
-      </c>
-      <c r="E70" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>912</v>
-      </c>
-      <c r="B71" t="s">
-        <v>669</v>
-      </c>
-      <c r="C71" t="s">
-        <v>692</v>
-      </c>
-      <c r="D71" t="s">
-        <v>693</v>
-      </c>
-      <c r="E71" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>913</v>
-      </c>
-      <c r="B72" t="s">
-        <v>669</v>
-      </c>
-      <c r="C72" t="s">
-        <v>693</v>
-      </c>
-      <c r="D72" t="s">
-        <v>670</v>
-      </c>
-      <c r="E72" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>914</v>
-      </c>
-      <c r="B73" t="s">
-        <v>694</v>
-      </c>
-      <c r="C73" t="s">
-        <v>695</v>
-      </c>
-      <c r="D73" t="s">
-        <v>696</v>
-      </c>
-      <c r="E73" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>915</v>
-      </c>
-      <c r="B74" t="s">
-        <v>694</v>
-      </c>
-      <c r="C74" t="s">
-        <v>696</v>
-      </c>
-      <c r="D74" t="s">
-        <v>697</v>
-      </c>
-      <c r="E74" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>916</v>
-      </c>
-      <c r="B75" t="s">
-        <v>694</v>
-      </c>
-      <c r="C75" t="s">
-        <v>697</v>
-      </c>
-      <c r="D75" t="s">
-        <v>2</v>
-      </c>
-      <c r="E75" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>917</v>
-      </c>
-      <c r="B76" t="s">
-        <v>694</v>
-      </c>
-      <c r="C76" t="s">
-        <v>2</v>
-      </c>
-      <c r="D76" t="s">
-        <v>698</v>
-      </c>
-      <c r="E76" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>918</v>
-      </c>
-      <c r="B77" t="s">
-        <v>694</v>
-      </c>
-      <c r="C77" t="s">
-        <v>698</v>
-      </c>
-      <c r="D77" t="s">
-        <v>278</v>
-      </c>
-      <c r="E77" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>919</v>
-      </c>
-      <c r="B78" t="s">
-        <v>694</v>
-      </c>
-      <c r="C78" t="s">
-        <v>278</v>
-      </c>
-      <c r="D78" t="s">
-        <v>699</v>
-      </c>
-      <c r="E78" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>920</v>
-      </c>
-      <c r="B79" t="s">
-        <v>694</v>
-      </c>
-      <c r="C79" t="s">
-        <v>699</v>
-      </c>
-      <c r="D79" t="s">
-        <v>700</v>
-      </c>
-      <c r="E79" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>921</v>
-      </c>
-      <c r="B80" t="s">
-        <v>694</v>
-      </c>
-      <c r="C80" t="s">
-        <v>700</v>
-      </c>
-      <c r="D80" t="s">
-        <v>701</v>
-      </c>
-      <c r="E80" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>922</v>
-      </c>
-      <c r="B81" t="s">
-        <v>694</v>
-      </c>
-      <c r="C81" t="s">
-        <v>701</v>
-      </c>
-      <c r="D81" t="s">
-        <v>702</v>
-      </c>
-      <c r="E81" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>923</v>
-      </c>
-      <c r="B82" t="s">
-        <v>694</v>
-      </c>
-      <c r="C82" t="s">
-        <v>702</v>
-      </c>
-      <c r="D82" t="s">
-        <v>703</v>
-      </c>
-      <c r="E82" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>924</v>
-      </c>
-      <c r="B83" t="s">
-        <v>694</v>
-      </c>
-      <c r="C83" t="s">
-        <v>703</v>
-      </c>
-      <c r="D83" t="s">
-        <v>5</v>
-      </c>
-      <c r="E83" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>925</v>
-      </c>
-      <c r="B84" t="s">
-        <v>694</v>
-      </c>
-      <c r="C84" t="s">
-        <v>5</v>
-      </c>
-      <c r="D84" t="s">
-        <v>11</v>
-      </c>
-      <c r="E84" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>926</v>
-      </c>
-      <c r="B85" t="s">
-        <v>694</v>
-      </c>
-      <c r="C85" t="s">
-        <v>11</v>
-      </c>
-      <c r="D85" t="s">
-        <v>704</v>
-      </c>
-      <c r="E85" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>927</v>
-      </c>
-      <c r="B86" t="s">
-        <v>694</v>
-      </c>
-      <c r="C86" t="s">
-        <v>704</v>
-      </c>
-      <c r="D86" t="s">
-        <v>705</v>
-      </c>
-      <c r="E86" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>928</v>
-      </c>
-      <c r="B87" t="s">
-        <v>694</v>
-      </c>
-      <c r="C87" t="s">
-        <v>705</v>
-      </c>
-      <c r="D87" t="s">
-        <v>706</v>
-      </c>
-      <c r="E87" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>929</v>
-      </c>
-      <c r="B88" t="s">
-        <v>694</v>
-      </c>
-      <c r="C88" t="s">
-        <v>706</v>
-      </c>
-      <c r="D88" t="s">
-        <v>707</v>
-      </c>
-      <c r="E88" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>930</v>
-      </c>
-      <c r="B89" t="s">
-        <v>694</v>
-      </c>
-      <c r="C89" t="s">
-        <v>707</v>
-      </c>
-      <c r="D89" t="s">
-        <v>708</v>
-      </c>
-      <c r="E89" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>931</v>
-      </c>
-      <c r="B90" t="s">
-        <v>694</v>
-      </c>
-      <c r="C90" t="s">
-        <v>708</v>
-      </c>
-      <c r="D90" t="s">
-        <v>709</v>
-      </c>
-      <c r="E90" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>932</v>
-      </c>
-      <c r="B91" t="s">
-        <v>694</v>
-      </c>
-      <c r="C91" t="s">
-        <v>709</v>
-      </c>
-      <c r="D91" t="s">
-        <v>710</v>
-      </c>
-      <c r="E91" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>933</v>
-      </c>
-      <c r="B92" t="s">
-        <v>694</v>
-      </c>
-      <c r="C92" t="s">
-        <v>710</v>
-      </c>
-      <c r="D92" t="s">
-        <v>711</v>
-      </c>
-      <c r="E92" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>934</v>
-      </c>
-      <c r="B93" t="s">
-        <v>694</v>
-      </c>
-      <c r="C93" t="s">
-        <v>711</v>
-      </c>
-      <c r="D93" t="s">
-        <v>712</v>
-      </c>
-      <c r="E93" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>935</v>
-      </c>
-      <c r="B94" t="s">
-        <v>694</v>
-      </c>
-      <c r="C94" t="s">
-        <v>712</v>
-      </c>
-      <c r="D94" t="s">
-        <v>713</v>
-      </c>
-      <c r="E94" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>936</v>
-      </c>
-      <c r="B95" t="s">
-        <v>694</v>
-      </c>
-      <c r="C95" t="s">
-        <v>713</v>
-      </c>
-      <c r="D95" t="s">
-        <v>23</v>
-      </c>
-      <c r="E95" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>937</v>
-      </c>
-      <c r="B96" t="s">
-        <v>694</v>
-      </c>
-      <c r="C96" t="s">
-        <v>23</v>
-      </c>
-      <c r="D96" t="s">
-        <v>714</v>
-      </c>
-      <c r="E96" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>938</v>
-      </c>
-      <c r="B97" t="s">
-        <v>694</v>
-      </c>
-      <c r="C97" t="s">
-        <v>714</v>
-      </c>
-      <c r="D97" t="s">
-        <v>715</v>
-      </c>
-      <c r="E97" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>939</v>
-      </c>
-      <c r="B98" t="s">
-        <v>694</v>
-      </c>
-      <c r="C98" t="s">
-        <v>715</v>
-      </c>
-      <c r="D98" t="s">
-        <v>716</v>
-      </c>
-      <c r="E98" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>940</v>
-      </c>
-      <c r="B99" t="s">
-        <v>694</v>
-      </c>
-      <c r="C99" t="s">
-        <v>716</v>
-      </c>
-      <c r="D99" t="s">
-        <v>717</v>
-      </c>
-      <c r="E99" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>941</v>
-      </c>
-      <c r="B100" t="s">
-        <v>694</v>
-      </c>
-      <c r="C100" t="s">
-        <v>717</v>
-      </c>
-      <c r="D100" t="s">
-        <v>718</v>
-      </c>
-      <c r="E100" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>942</v>
-      </c>
-      <c r="B101" t="s">
-        <v>694</v>
-      </c>
-      <c r="C101" t="s">
-        <v>718</v>
-      </c>
-      <c r="D101" t="s">
-        <v>719</v>
-      </c>
-      <c r="E101" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>943</v>
-      </c>
-      <c r="B102" t="s">
-        <v>694</v>
-      </c>
-      <c r="C102" t="s">
-        <v>719</v>
-      </c>
-      <c r="D102" t="s">
-        <v>720</v>
-      </c>
-      <c r="E102" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>944</v>
-      </c>
-      <c r="B103" t="s">
-        <v>694</v>
-      </c>
-      <c r="C103" t="s">
-        <v>720</v>
-      </c>
-      <c r="D103" t="s">
-        <v>721</v>
-      </c>
-      <c r="E103" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>945</v>
-      </c>
-      <c r="B104" t="s">
-        <v>694</v>
-      </c>
-      <c r="C104" t="s">
-        <v>721</v>
-      </c>
-      <c r="D104" t="s">
-        <v>722</v>
-      </c>
-      <c r="E104" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>946</v>
-      </c>
-      <c r="B105" t="s">
-        <v>694</v>
-      </c>
-      <c r="C105" t="s">
-        <v>722</v>
-      </c>
-      <c r="D105" t="s">
-        <v>723</v>
-      </c>
-      <c r="E105" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>947</v>
-      </c>
-      <c r="B106" t="s">
-        <v>694</v>
-      </c>
-      <c r="C106" t="s">
-        <v>723</v>
-      </c>
-      <c r="D106" t="s">
-        <v>724</v>
-      </c>
-      <c r="E106" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>948</v>
-      </c>
-      <c r="B107" t="s">
-        <v>694</v>
-      </c>
-      <c r="C107" t="s">
-        <v>724</v>
-      </c>
-      <c r="D107" t="s">
-        <v>725</v>
-      </c>
-      <c r="E107" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>949</v>
-      </c>
-      <c r="B108" t="s">
-        <v>694</v>
-      </c>
-      <c r="C108" t="s">
-        <v>725</v>
-      </c>
-      <c r="D108" t="s">
-        <v>726</v>
-      </c>
-      <c r="E108" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>950</v>
-      </c>
-      <c r="B109" t="s">
-        <v>694</v>
-      </c>
-      <c r="C109" t="s">
-        <v>726</v>
-      </c>
-      <c r="D109" t="s">
-        <v>727</v>
-      </c>
-      <c r="E109" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
-        <v>951</v>
-      </c>
-      <c r="B110" t="s">
-        <v>694</v>
-      </c>
-      <c r="C110" t="s">
-        <v>727</v>
-      </c>
-      <c r="D110" t="s">
-        <v>8</v>
-      </c>
-      <c r="E110" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>952</v>
-      </c>
-      <c r="B111" t="s">
-        <v>694</v>
-      </c>
-      <c r="C111" t="s">
-        <v>8</v>
-      </c>
-      <c r="D111" t="s">
-        <v>271</v>
-      </c>
-      <c r="E111" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>953</v>
-      </c>
-      <c r="B112" t="s">
-        <v>694</v>
-      </c>
-      <c r="C112" t="s">
-        <v>271</v>
-      </c>
-      <c r="D112" t="s">
-        <v>274</v>
-      </c>
-      <c r="E112" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>954</v>
-      </c>
-      <c r="B113" t="s">
-        <v>694</v>
-      </c>
-      <c r="C113" t="s">
-        <v>274</v>
-      </c>
-      <c r="D113" t="s">
-        <v>728</v>
-      </c>
-      <c r="E113" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
-        <v>955</v>
-      </c>
-      <c r="B114" t="s">
-        <v>694</v>
-      </c>
-      <c r="C114" t="s">
-        <v>728</v>
-      </c>
-      <c r="D114" t="s">
-        <v>729</v>
-      </c>
-      <c r="E114" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>956</v>
-      </c>
-      <c r="B115" t="s">
-        <v>694</v>
-      </c>
-      <c r="C115" t="s">
-        <v>729</v>
-      </c>
-      <c r="D115" t="s">
-        <v>695</v>
-      </c>
-      <c r="E115" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>957</v>
-      </c>
-      <c r="B116" t="s">
-        <v>730</v>
-      </c>
-      <c r="C116" t="s">
-        <v>731</v>
-      </c>
-      <c r="D116" t="s">
-        <v>732</v>
-      </c>
-      <c r="E116" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
-        <v>958</v>
-      </c>
-      <c r="B117" t="s">
-        <v>730</v>
-      </c>
-      <c r="C117" t="s">
-        <v>732</v>
-      </c>
-      <c r="D117" t="s">
-        <v>733</v>
-      </c>
-      <c r="E117" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
-        <v>959</v>
-      </c>
-      <c r="B118" t="s">
-        <v>730</v>
-      </c>
-      <c r="C118" t="s">
-        <v>733</v>
-      </c>
-      <c r="D118" t="s">
-        <v>734</v>
-      </c>
-      <c r="E118" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
-        <v>960</v>
-      </c>
-      <c r="B119" t="s">
-        <v>730</v>
-      </c>
-      <c r="C119" t="s">
-        <v>734</v>
-      </c>
-      <c r="D119" t="s">
-        <v>735</v>
-      </c>
-      <c r="E119" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
-        <v>961</v>
-      </c>
-      <c r="B120" t="s">
-        <v>730</v>
-      </c>
-      <c r="C120" t="s">
-        <v>735</v>
-      </c>
-      <c r="D120" t="s">
-        <v>736</v>
-      </c>
-      <c r="E120" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
-        <v>962</v>
-      </c>
-      <c r="B121" t="s">
-        <v>730</v>
-      </c>
-      <c r="C121" t="s">
-        <v>736</v>
-      </c>
-      <c r="D121" t="s">
-        <v>737</v>
-      </c>
-      <c r="E121" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>963</v>
-      </c>
-      <c r="B122" t="s">
-        <v>730</v>
-      </c>
-      <c r="C122" t="s">
-        <v>737</v>
-      </c>
-      <c r="D122" t="s">
-        <v>738</v>
-      </c>
-      <c r="E122" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
-        <v>964</v>
-      </c>
-      <c r="B123" t="s">
-        <v>730</v>
-      </c>
-      <c r="C123" t="s">
-        <v>738</v>
-      </c>
-      <c r="D123" t="s">
-        <v>739</v>
-      </c>
-      <c r="E123" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
-        <v>965</v>
-      </c>
-      <c r="B124" t="s">
-        <v>730</v>
-      </c>
-      <c r="C124" t="s">
-        <v>739</v>
-      </c>
-      <c r="D124" t="s">
-        <v>740</v>
-      </c>
-      <c r="E124" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
-        <v>966</v>
-      </c>
-      <c r="B125" t="s">
-        <v>730</v>
-      </c>
-      <c r="C125" t="s">
-        <v>740</v>
-      </c>
-      <c r="D125" t="s">
-        <v>741</v>
-      </c>
-      <c r="E125" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
-        <v>967</v>
-      </c>
-      <c r="B126" t="s">
-        <v>730</v>
-      </c>
-      <c r="C126" t="s">
-        <v>741</v>
-      </c>
-      <c r="D126" t="s">
-        <v>742</v>
-      </c>
-      <c r="E126" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>968</v>
-      </c>
-      <c r="B127" t="s">
-        <v>730</v>
-      </c>
-      <c r="C127" t="s">
-        <v>742</v>
-      </c>
-      <c r="D127" t="s">
-        <v>743</v>
-      </c>
-      <c r="E127" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
-        <v>969</v>
-      </c>
-      <c r="B128" t="s">
-        <v>730</v>
-      </c>
-      <c r="C128" t="s">
-        <v>743</v>
-      </c>
-      <c r="D128" t="s">
-        <v>744</v>
-      </c>
-      <c r="E128" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
-        <v>970</v>
-      </c>
-      <c r="B129" t="s">
-        <v>745</v>
-      </c>
-      <c r="C129" t="s">
-        <v>746</v>
-      </c>
-      <c r="D129" t="s">
-        <v>747</v>
-      </c>
-      <c r="E129" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
-        <v>971</v>
-      </c>
-      <c r="B130" t="s">
-        <v>745</v>
-      </c>
-      <c r="C130" t="s">
-        <v>747</v>
-      </c>
-      <c r="D130" t="s">
-        <v>748</v>
-      </c>
-      <c r="E130" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>972</v>
-      </c>
-      <c r="B131" t="s">
-        <v>745</v>
-      </c>
-      <c r="C131" t="s">
-        <v>748</v>
-      </c>
-      <c r="D131" t="s">
-        <v>749</v>
-      </c>
-      <c r="E131" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
-        <v>973</v>
-      </c>
-      <c r="B132" t="s">
-        <v>745</v>
-      </c>
-      <c r="C132" t="s">
-        <v>749</v>
-      </c>
-      <c r="D132" t="s">
-        <v>750</v>
-      </c>
-      <c r="E132" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
-        <v>974</v>
-      </c>
-      <c r="B133" t="s">
-        <v>745</v>
-      </c>
-      <c r="C133" t="s">
-        <v>750</v>
-      </c>
-      <c r="D133" t="s">
-        <v>751</v>
-      </c>
-      <c r="E133" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>975</v>
-      </c>
-      <c r="B134" t="s">
-        <v>745</v>
-      </c>
-      <c r="C134" t="s">
-        <v>751</v>
-      </c>
-      <c r="D134" t="s">
-        <v>752</v>
-      </c>
-      <c r="E134" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
-        <v>976</v>
-      </c>
-      <c r="B135" t="s">
-        <v>745</v>
-      </c>
-      <c r="C135" t="s">
-        <v>752</v>
-      </c>
-      <c r="D135" t="s">
-        <v>753</v>
-      </c>
-      <c r="E135" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
-        <v>977</v>
-      </c>
-      <c r="B136" t="s">
-        <v>745</v>
-      </c>
-      <c r="C136" t="s">
-        <v>753</v>
-      </c>
-      <c r="D136" t="s">
-        <v>754</v>
-      </c>
-      <c r="E136" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
-        <v>978</v>
-      </c>
-      <c r="B137" t="s">
-        <v>745</v>
-      </c>
-      <c r="C137" t="s">
-        <v>754</v>
-      </c>
-      <c r="D137" t="s">
-        <v>755</v>
-      </c>
-      <c r="E137" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>979</v>
-      </c>
-      <c r="B138" t="s">
-        <v>745</v>
-      </c>
-      <c r="C138" t="s">
-        <v>755</v>
-      </c>
-      <c r="D138" t="s">
-        <v>756</v>
-      </c>
-      <c r="E138" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
-        <v>980</v>
-      </c>
-      <c r="B139" t="s">
-        <v>745</v>
-      </c>
-      <c r="C139" t="s">
-        <v>756</v>
-      </c>
-      <c r="D139" t="s">
-        <v>757</v>
-      </c>
-      <c r="E139" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>981</v>
-      </c>
-      <c r="B140" t="s">
-        <v>745</v>
-      </c>
-      <c r="C140" t="s">
-        <v>757</v>
-      </c>
-      <c r="D140" t="s">
-        <v>758</v>
-      </c>
-      <c r="E140" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
-        <v>982</v>
-      </c>
-      <c r="B141" t="s">
-        <v>745</v>
-      </c>
-      <c r="C141" t="s">
-        <v>758</v>
-      </c>
-      <c r="D141" t="s">
-        <v>759</v>
-      </c>
-      <c r="E141" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
-        <v>983</v>
-      </c>
-      <c r="B142" t="s">
-        <v>745</v>
-      </c>
-      <c r="C142" t="s">
-        <v>759</v>
-      </c>
-      <c r="D142" t="s">
-        <v>760</v>
-      </c>
-      <c r="E142" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
-        <v>984</v>
-      </c>
-      <c r="B143" t="s">
-        <v>745</v>
-      </c>
-      <c r="C143" t="s">
-        <v>760</v>
-      </c>
-      <c r="D143" t="s">
-        <v>761</v>
-      </c>
-      <c r="E143" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
-        <v>985</v>
-      </c>
-      <c r="B144" t="s">
-        <v>745</v>
-      </c>
-      <c r="C144" t="s">
-        <v>761</v>
-      </c>
-      <c r="D144" t="s">
-        <v>762</v>
-      </c>
-      <c r="E144" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
-        <v>986</v>
-      </c>
-      <c r="B145" t="s">
-        <v>745</v>
-      </c>
-      <c r="C145" t="s">
-        <v>762</v>
-      </c>
-      <c r="D145" t="s">
-        <v>763</v>
-      </c>
-      <c r="E145" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
-        <v>987</v>
-      </c>
-      <c r="B146" t="s">
-        <v>745</v>
-      </c>
-      <c r="C146" t="s">
-        <v>763</v>
-      </c>
-      <c r="D146" t="s">
-        <v>764</v>
-      </c>
-      <c r="E146" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
-        <v>988</v>
-      </c>
-      <c r="B147" t="s">
-        <v>745</v>
-      </c>
-      <c r="C147" t="s">
-        <v>764</v>
-      </c>
-      <c r="D147" t="s">
-        <v>765</v>
-      </c>
-      <c r="E147" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
-        <v>989</v>
-      </c>
-      <c r="B148" t="s">
-        <v>745</v>
-      </c>
-      <c r="C148" t="s">
-        <v>765</v>
-      </c>
-      <c r="D148" t="s">
-        <v>766</v>
-      </c>
-      <c r="E148" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
-        <v>990</v>
-      </c>
-      <c r="B149" t="s">
-        <v>745</v>
-      </c>
-      <c r="C149" t="s">
-        <v>766</v>
-      </c>
-      <c r="D149" t="s">
-        <v>767</v>
-      </c>
-      <c r="E149" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
-        <v>991</v>
-      </c>
-      <c r="B150" t="s">
-        <v>745</v>
-      </c>
-      <c r="C150" t="s">
-        <v>767</v>
-      </c>
-      <c r="D150" t="s">
-        <v>768</v>
-      </c>
-      <c r="E150" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
-        <v>992</v>
-      </c>
-      <c r="B151" t="s">
-        <v>745</v>
-      </c>
-      <c r="C151" t="s">
-        <v>768</v>
-      </c>
-      <c r="D151" t="s">
-        <v>769</v>
-      </c>
-      <c r="E151" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A152" t="s">
-        <v>993</v>
-      </c>
-      <c r="B152" t="s">
-        <v>745</v>
-      </c>
-      <c r="C152" t="s">
-        <v>769</v>
-      </c>
-      <c r="D152" t="s">
-        <v>770</v>
-      </c>
-      <c r="E152" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
-        <v>994</v>
-      </c>
-      <c r="B153" t="s">
-        <v>745</v>
-      </c>
-      <c r="C153" t="s">
-        <v>770</v>
-      </c>
-      <c r="D153" t="s">
-        <v>771</v>
-      </c>
-      <c r="E153" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A154" t="s">
-        <v>995</v>
-      </c>
-      <c r="B154" t="s">
-        <v>745</v>
-      </c>
-      <c r="C154" t="s">
-        <v>771</v>
-      </c>
-      <c r="D154" t="s">
-        <v>772</v>
-      </c>
-      <c r="E154" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
-        <v>996</v>
-      </c>
-      <c r="B155" t="s">
-        <v>745</v>
-      </c>
-      <c r="C155" t="s">
-        <v>772</v>
-      </c>
-      <c r="D155" t="s">
-        <v>773</v>
-      </c>
-      <c r="E155" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
-        <v>997</v>
-      </c>
-      <c r="B156" t="s">
-        <v>745</v>
-      </c>
-      <c r="C156" t="s">
-        <v>773</v>
-      </c>
-      <c r="D156" t="s">
-        <v>774</v>
-      </c>
-      <c r="E156" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
-        <v>998</v>
-      </c>
-      <c r="B157" t="s">
-        <v>745</v>
-      </c>
-      <c r="C157" t="s">
-        <v>774</v>
-      </c>
-      <c r="D157" t="s">
-        <v>775</v>
-      </c>
-      <c r="E157" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
-        <v>999</v>
-      </c>
-      <c r="B158" t="s">
-        <v>745</v>
-      </c>
-      <c r="C158" t="s">
-        <v>775</v>
-      </c>
-      <c r="D158" t="s">
-        <v>776</v>
-      </c>
-      <c r="E158" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A159" t="s">
-        <v>1000</v>
-      </c>
-      <c r="B159" t="s">
-        <v>745</v>
-      </c>
-      <c r="C159" t="s">
-        <v>776</v>
-      </c>
-      <c r="D159" t="s">
-        <v>777</v>
-      </c>
-      <c r="E159" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A160" t="s">
-        <v>1001</v>
-      </c>
-      <c r="B160" t="s">
-        <v>745</v>
-      </c>
-      <c r="C160" t="s">
-        <v>777</v>
-      </c>
-      <c r="D160" t="s">
-        <v>778</v>
-      </c>
-      <c r="E160" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A161" t="s">
-        <v>1002</v>
-      </c>
-      <c r="B161" t="s">
-        <v>779</v>
-      </c>
-      <c r="C161" t="s">
-        <v>260</v>
-      </c>
-      <c r="D161" t="s">
-        <v>780</v>
-      </c>
-      <c r="E161" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A162" t="s">
-        <v>1003</v>
-      </c>
-      <c r="B162" t="s">
-        <v>779</v>
-      </c>
-      <c r="C162" t="s">
-        <v>780</v>
-      </c>
-      <c r="D162" t="s">
-        <v>781</v>
-      </c>
-      <c r="E162" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A163" t="s">
-        <v>1004</v>
-      </c>
-      <c r="B163" t="s">
-        <v>779</v>
-      </c>
-      <c r="C163" t="s">
-        <v>781</v>
-      </c>
-      <c r="D163" t="s">
-        <v>782</v>
-      </c>
-      <c r="E163" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
-        <v>1005</v>
-      </c>
-      <c r="B164" t="s">
-        <v>779</v>
-      </c>
-      <c r="C164" t="s">
-        <v>782</v>
-      </c>
-      <c r="D164" t="s">
-        <v>783</v>
-      </c>
-      <c r="E164" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A165" t="s">
-        <v>1006</v>
-      </c>
-      <c r="B165" t="s">
-        <v>779</v>
-      </c>
-      <c r="C165" t="s">
-        <v>783</v>
-      </c>
-      <c r="D165" t="s">
-        <v>785</v>
-      </c>
-      <c r="E165" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A166" t="s">
-        <v>1007</v>
-      </c>
-      <c r="B166" t="s">
-        <v>779</v>
-      </c>
-      <c r="C166" t="s">
-        <v>785</v>
-      </c>
-      <c r="D166" t="s">
-        <v>787</v>
-      </c>
-      <c r="E166" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A167" t="s">
-        <v>1008</v>
-      </c>
-      <c r="B167" t="s">
-        <v>779</v>
-      </c>
-      <c r="C167" t="s">
-        <v>787</v>
-      </c>
-      <c r="D167" t="s">
-        <v>788</v>
-      </c>
-      <c r="E167" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
-        <v>1009</v>
-      </c>
-      <c r="B168" t="s">
-        <v>779</v>
-      </c>
-      <c r="C168" t="s">
-        <v>788</v>
-      </c>
-      <c r="D168" t="s">
-        <v>789</v>
-      </c>
-      <c r="E168" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
-        <v>1010</v>
-      </c>
-      <c r="B169" t="s">
-        <v>779</v>
-      </c>
-      <c r="C169" t="s">
-        <v>789</v>
-      </c>
-      <c r="D169" t="s">
-        <v>790</v>
-      </c>
-      <c r="E169" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
-        <v>1011</v>
-      </c>
-      <c r="B170" t="s">
-        <v>779</v>
-      </c>
-      <c r="C170" t="s">
-        <v>790</v>
-      </c>
-      <c r="D170" t="s">
-        <v>31</v>
-      </c>
-      <c r="E170" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
-        <v>1012</v>
-      </c>
-      <c r="B171" t="s">
-        <v>779</v>
-      </c>
-      <c r="C171" t="s">
-        <v>31</v>
-      </c>
-      <c r="D171" t="s">
-        <v>232</v>
-      </c>
-      <c r="E171" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
-        <v>1013</v>
-      </c>
-      <c r="B172" t="s">
-        <v>779</v>
-      </c>
-      <c r="C172" t="s">
-        <v>232</v>
-      </c>
-      <c r="D172" t="s">
-        <v>791</v>
-      </c>
-      <c r="E172" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A173" t="s">
-        <v>1014</v>
-      </c>
-      <c r="B173" t="s">
-        <v>779</v>
-      </c>
-      <c r="C173" t="s">
-        <v>791</v>
-      </c>
-      <c r="D173" t="s">
-        <v>792</v>
-      </c>
-      <c r="E173" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A174" t="s">
-        <v>1015</v>
-      </c>
-      <c r="B174" t="s">
-        <v>779</v>
-      </c>
-      <c r="C174" t="s">
-        <v>792</v>
-      </c>
-      <c r="D174" t="s">
-        <v>793</v>
-      </c>
-      <c r="E174" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A175" t="s">
-        <v>1016</v>
-      </c>
-      <c r="B175" t="s">
-        <v>779</v>
-      </c>
-      <c r="C175" t="s">
-        <v>793</v>
-      </c>
-      <c r="D175" t="s">
-        <v>794</v>
-      </c>
-      <c r="E175" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A176" t="s">
-        <v>1017</v>
-      </c>
-      <c r="B176" t="s">
-        <v>779</v>
-      </c>
-      <c r="C176" t="s">
-        <v>794</v>
-      </c>
-      <c r="D176" t="s">
-        <v>28</v>
-      </c>
-      <c r="E176" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A177" t="s">
-        <v>1018</v>
-      </c>
-      <c r="B177" t="s">
-        <v>779</v>
-      </c>
-      <c r="C177" t="s">
-        <v>28</v>
-      </c>
-      <c r="D177" t="s">
-        <v>634</v>
-      </c>
-      <c r="E177" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A178" t="s">
-        <v>1019</v>
-      </c>
-      <c r="B178" t="s">
-        <v>779</v>
-      </c>
-      <c r="C178" t="s">
-        <v>634</v>
-      </c>
-      <c r="D178" t="s">
-        <v>795</v>
-      </c>
-      <c r="E178" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A179" t="s">
-        <v>1020</v>
-      </c>
-      <c r="B179" t="s">
-        <v>779</v>
-      </c>
-      <c r="C179" t="s">
-        <v>795</v>
-      </c>
-      <c r="D179" t="s">
-        <v>796</v>
-      </c>
-      <c r="E179" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A180" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B180" t="s">
-        <v>779</v>
-      </c>
-      <c r="C180" t="s">
-        <v>796</v>
-      </c>
-      <c r="D180" t="s">
-        <v>797</v>
-      </c>
-      <c r="E180" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A181" t="s">
-        <v>1022</v>
-      </c>
-      <c r="B181" t="s">
-        <v>779</v>
-      </c>
-      <c r="C181" t="s">
-        <v>797</v>
-      </c>
-      <c r="D181" t="s">
-        <v>798</v>
-      </c>
-      <c r="E181" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A182" t="s">
-        <v>1023</v>
-      </c>
-      <c r="B182" t="s">
-        <v>779</v>
-      </c>
-      <c r="C182" t="s">
-        <v>798</v>
-      </c>
-      <c r="D182" t="s">
-        <v>799</v>
-      </c>
-      <c r="E182" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A183" t="s">
-        <v>1024</v>
-      </c>
-      <c r="B183" t="s">
-        <v>779</v>
-      </c>
-      <c r="C183" t="s">
-        <v>799</v>
-      </c>
-      <c r="D183" t="s">
-        <v>800</v>
-      </c>
-      <c r="E183" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
-        <v>1025</v>
-      </c>
-      <c r="B184" t="s">
-        <v>779</v>
-      </c>
-      <c r="C184" t="s">
-        <v>800</v>
-      </c>
-      <c r="D184" t="s">
-        <v>801</v>
-      </c>
-      <c r="E184" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A185" t="s">
-        <v>1026</v>
-      </c>
-      <c r="B185" t="s">
-        <v>779</v>
-      </c>
-      <c r="C185" t="s">
-        <v>801</v>
-      </c>
-      <c r="D185" t="s">
-        <v>262</v>
-      </c>
-      <c r="E185" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A186" t="s">
-        <v>1027</v>
-      </c>
-      <c r="B186" t="s">
-        <v>802</v>
-      </c>
-      <c r="C186" t="s">
-        <v>801</v>
-      </c>
-      <c r="D186" t="s">
-        <v>273</v>
-      </c>
-      <c r="E186" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A187" t="s">
-        <v>1028</v>
-      </c>
-      <c r="B187" t="s">
-        <v>802</v>
-      </c>
-      <c r="C187" t="s">
-        <v>273</v>
-      </c>
-      <c r="D187" t="s">
-        <v>803</v>
-      </c>
-      <c r="E187" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A188" t="s">
-        <v>1029</v>
-      </c>
-      <c r="B188" t="s">
-        <v>802</v>
-      </c>
-      <c r="C188" t="s">
-        <v>803</v>
-      </c>
-      <c r="D188" t="s">
-        <v>11</v>
-      </c>
-      <c r="E188" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A189" t="s">
-        <v>1030</v>
-      </c>
-      <c r="B189" t="s">
-        <v>802</v>
-      </c>
-      <c r="C189" t="s">
-        <v>11</v>
-      </c>
-      <c r="D189" t="s">
-        <v>720</v>
-      </c>
-      <c r="E189" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A190" t="s">
-        <v>1031</v>
-      </c>
-      <c r="B190" t="s">
-        <v>802</v>
-      </c>
-      <c r="C190" t="s">
-        <v>720</v>
-      </c>
-      <c r="D190" t="s">
-        <v>804</v>
-      </c>
-      <c r="E190" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A191" t="s">
-        <v>1032</v>
-      </c>
-      <c r="B191" t="s">
-        <v>802</v>
-      </c>
-      <c r="C191" t="s">
-        <v>804</v>
-      </c>
-      <c r="D191" t="s">
-        <v>300</v>
-      </c>
-      <c r="E191" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A192" t="s">
-        <v>1033</v>
-      </c>
-      <c r="B192" t="s">
-        <v>802</v>
-      </c>
-      <c r="C192" t="s">
-        <v>300</v>
-      </c>
-      <c r="D192" t="s">
-        <v>303</v>
-      </c>
-      <c r="E192" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A193" t="s">
-        <v>1034</v>
-      </c>
-      <c r="B193" t="s">
-        <v>802</v>
-      </c>
-      <c r="C193" t="s">
-        <v>303</v>
-      </c>
-      <c r="D193" t="s">
-        <v>805</v>
-      </c>
-      <c r="E193" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A194" t="s">
-        <v>1035</v>
-      </c>
-      <c r="B194" t="s">
-        <v>802</v>
-      </c>
-      <c r="C194" t="s">
-        <v>805</v>
-      </c>
-      <c r="D194" t="s">
-        <v>806</v>
-      </c>
-      <c r="E194" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A195" t="s">
-        <v>1036</v>
-      </c>
-      <c r="B195" t="s">
-        <v>802</v>
-      </c>
-      <c r="C195" t="s">
-        <v>806</v>
-      </c>
-      <c r="D195" t="s">
-        <v>807</v>
-      </c>
-      <c r="E195" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A196" t="s">
-        <v>1037</v>
-      </c>
-      <c r="B196" t="s">
-        <v>802</v>
-      </c>
-      <c r="C196" t="s">
-        <v>807</v>
-      </c>
-      <c r="D196" t="s">
-        <v>808</v>
-      </c>
-      <c r="E196" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A197" t="s">
-        <v>1038</v>
-      </c>
-      <c r="B197" t="s">
-        <v>802</v>
-      </c>
-      <c r="C197" t="s">
-        <v>808</v>
-      </c>
-      <c r="D197" t="s">
-        <v>809</v>
-      </c>
-      <c r="E197" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A198" t="s">
-        <v>1039</v>
-      </c>
-      <c r="B198" t="s">
-        <v>802</v>
-      </c>
-      <c r="C198" t="s">
-        <v>809</v>
-      </c>
-      <c r="D198" t="s">
-        <v>810</v>
-      </c>
-      <c r="E198" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A199" t="s">
-        <v>1040</v>
-      </c>
-      <c r="B199" t="s">
-        <v>802</v>
-      </c>
-      <c r="C199" t="s">
-        <v>810</v>
-      </c>
-      <c r="D199" t="s">
-        <v>811</v>
-      </c>
-      <c r="E199" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A200" t="s">
-        <v>1041</v>
-      </c>
-      <c r="B200" t="s">
-        <v>802</v>
-      </c>
-      <c r="C200" t="s">
-        <v>811</v>
-      </c>
-      <c r="D200" t="s">
-        <v>812</v>
-      </c>
-      <c r="E200" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A201" t="s">
-        <v>1042</v>
-      </c>
-      <c r="B201" t="s">
-        <v>802</v>
-      </c>
-      <c r="C201" t="s">
-        <v>812</v>
-      </c>
-      <c r="D201" t="s">
-        <v>813</v>
-      </c>
-      <c r="E201" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A202" t="s">
-        <v>1043</v>
-      </c>
-      <c r="B202" t="s">
-        <v>802</v>
-      </c>
-      <c r="C202" t="s">
-        <v>813</v>
-      </c>
-      <c r="D202" t="s">
-        <v>814</v>
-      </c>
-      <c r="E202" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A203" t="s">
-        <v>1044</v>
-      </c>
-      <c r="B203" t="s">
-        <v>802</v>
-      </c>
-      <c r="C203" t="s">
-        <v>814</v>
-      </c>
-      <c r="D203" t="s">
-        <v>815</v>
-      </c>
-      <c r="E203" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A204" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B204" t="s">
-        <v>802</v>
-      </c>
-      <c r="C204" t="s">
-        <v>815</v>
-      </c>
-      <c r="D204" t="s">
-        <v>744</v>
-      </c>
-      <c r="E204" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A205" t="s">
-        <v>1046</v>
-      </c>
-      <c r="B205" t="s">
-        <v>802</v>
-      </c>
-      <c r="C205" t="s">
-        <v>744</v>
-      </c>
-      <c r="D205" t="s">
-        <v>816</v>
-      </c>
-      <c r="E205" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A206" t="s">
-        <v>1047</v>
-      </c>
-      <c r="B206" t="s">
-        <v>802</v>
-      </c>
-      <c r="C206" t="s">
-        <v>816</v>
-      </c>
-      <c r="D206" t="s">
-        <v>682</v>
-      </c>
-      <c r="E206" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A207" t="s">
-        <v>1048</v>
-      </c>
-      <c r="B207" t="s">
-        <v>802</v>
-      </c>
-      <c r="C207" t="s">
-        <v>682</v>
-      </c>
-      <c r="D207" t="s">
-        <v>817</v>
-      </c>
-      <c r="E207" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A208" t="s">
-        <v>1049</v>
-      </c>
-      <c r="B208" t="s">
-        <v>802</v>
-      </c>
-      <c r="C208" t="s">
-        <v>817</v>
-      </c>
-      <c r="D208" t="s">
-        <v>818</v>
-      </c>
-      <c r="E208" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A209" t="s">
-        <v>1050</v>
-      </c>
-      <c r="B209" t="s">
-        <v>802</v>
-      </c>
-      <c r="C209" t="s">
-        <v>818</v>
-      </c>
-      <c r="D209" t="s">
-        <v>801</v>
-      </c>
-      <c r="E209" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A210" t="s">
-        <v>1051</v>
-      </c>
-      <c r="B210" t="s">
-        <v>819</v>
-      </c>
-      <c r="C210" t="s">
-        <v>780</v>
-      </c>
-      <c r="D210" t="s">
-        <v>630</v>
-      </c>
-      <c r="E210" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A211" t="s">
-        <v>1052</v>
-      </c>
-      <c r="B211" t="s">
-        <v>819</v>
-      </c>
-      <c r="C211" t="s">
-        <v>630</v>
-      </c>
-      <c r="D211" t="s">
-        <v>820</v>
-      </c>
-      <c r="E211" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A212" t="s">
-        <v>1053</v>
-      </c>
-      <c r="B212" t="s">
-        <v>819</v>
-      </c>
-      <c r="C212" t="s">
-        <v>820</v>
-      </c>
-      <c r="D212" t="s">
-        <v>821</v>
-      </c>
-      <c r="E212" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A213" t="s">
-        <v>1054</v>
-      </c>
-      <c r="B213" t="s">
-        <v>819</v>
-      </c>
-      <c r="C213" t="s">
-        <v>821</v>
-      </c>
-      <c r="D213" t="s">
-        <v>822</v>
-      </c>
-      <c r="E213" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A214" t="s">
-        <v>1055</v>
-      </c>
-      <c r="B214" t="s">
-        <v>819</v>
-      </c>
-      <c r="C214" t="s">
-        <v>822</v>
-      </c>
-      <c r="D214" t="s">
-        <v>270</v>
-      </c>
-      <c r="E214" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A215" t="s">
-        <v>1056</v>
-      </c>
-      <c r="B215" t="s">
-        <v>819</v>
-      </c>
-      <c r="C215" t="s">
-        <v>270</v>
-      </c>
-      <c r="D215" t="s">
-        <v>823</v>
-      </c>
-      <c r="E215" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A216" t="s">
-        <v>1057</v>
-      </c>
-      <c r="B216" t="s">
-        <v>819</v>
-      </c>
-      <c r="C216" t="s">
-        <v>823</v>
-      </c>
-      <c r="D216" t="s">
-        <v>8</v>
-      </c>
-      <c r="E216" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A217" t="s">
-        <v>1058</v>
-      </c>
-      <c r="B217" t="s">
-        <v>819</v>
-      </c>
-      <c r="C217" t="s">
-        <v>8</v>
-      </c>
-      <c r="D217" t="s">
-        <v>824</v>
-      </c>
-      <c r="E217" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A218" t="s">
-        <v>1059</v>
-      </c>
-      <c r="B218" t="s">
-        <v>819</v>
-      </c>
-      <c r="C218" t="s">
-        <v>824</v>
-      </c>
-      <c r="D218" t="s">
-        <v>825</v>
-      </c>
-      <c r="E218" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A219" t="s">
-        <v>1060</v>
-      </c>
-      <c r="B219" t="s">
-        <v>819</v>
-      </c>
-      <c r="C219" t="s">
-        <v>825</v>
-      </c>
-      <c r="D219" t="s">
-        <v>826</v>
-      </c>
-      <c r="E219" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A220" t="s">
-        <v>1061</v>
-      </c>
-      <c r="B220" t="s">
-        <v>819</v>
-      </c>
-      <c r="C220" t="s">
-        <v>826</v>
-      </c>
-      <c r="D220" t="s">
-        <v>803</v>
-      </c>
-      <c r="E220" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A221" t="s">
-        <v>1062</v>
-      </c>
-      <c r="B221" t="s">
-        <v>819</v>
-      </c>
-      <c r="C221" t="s">
-        <v>803</v>
-      </c>
-      <c r="D221" t="s">
-        <v>726</v>
-      </c>
-      <c r="E221" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A222" t="s">
-        <v>1063</v>
-      </c>
-      <c r="B222" t="s">
-        <v>819</v>
-      </c>
-      <c r="C222" t="s">
-        <v>726</v>
-      </c>
-      <c r="D222" t="s">
-        <v>827</v>
-      </c>
-      <c r="E222" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A223" t="s">
-        <v>1064</v>
-      </c>
-      <c r="B223" t="s">
-        <v>819</v>
-      </c>
-      <c r="C223" t="s">
-        <v>827</v>
-      </c>
-      <c r="D223" t="s">
-        <v>828</v>
-      </c>
-      <c r="E223" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A224" t="s">
-        <v>1065</v>
-      </c>
-      <c r="B224" t="s">
-        <v>819</v>
-      </c>
-      <c r="C224" t="s">
-        <v>828</v>
-      </c>
-      <c r="D224" t="s">
-        <v>829</v>
-      </c>
-      <c r="E224" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A225" t="s">
-        <v>1066</v>
-      </c>
-      <c r="B225" t="s">
-        <v>819</v>
-      </c>
-      <c r="C225" t="s">
-        <v>829</v>
-      </c>
-      <c r="D225" t="s">
-        <v>830</v>
-      </c>
-      <c r="E225" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A226" t="s">
-        <v>1067</v>
-      </c>
-      <c r="B226" t="s">
-        <v>819</v>
-      </c>
-      <c r="C226" t="s">
-        <v>830</v>
-      </c>
-      <c r="D226" t="s">
-        <v>831</v>
-      </c>
-      <c r="E226" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A227" t="s">
-        <v>1068</v>
-      </c>
-      <c r="B227" t="s">
-        <v>819</v>
-      </c>
-      <c r="C227" t="s">
-        <v>831</v>
-      </c>
-      <c r="D227" t="s">
-        <v>832</v>
-      </c>
-      <c r="E227" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A228" t="s">
-        <v>1069</v>
-      </c>
-      <c r="B228" t="s">
-        <v>819</v>
-      </c>
-      <c r="C228" t="s">
-        <v>832</v>
-      </c>
-      <c r="D228" t="s">
-        <v>833</v>
-      </c>
-      <c r="E228" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A229" t="s">
-        <v>1070</v>
-      </c>
-      <c r="B229" t="s">
-        <v>819</v>
-      </c>
-      <c r="C229" t="s">
-        <v>833</v>
-      </c>
-      <c r="D229" t="s">
-        <v>834</v>
-      </c>
-      <c r="E229" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A230" t="s">
-        <v>1071</v>
-      </c>
-      <c r="B230" t="s">
-        <v>819</v>
-      </c>
-      <c r="C230" t="s">
-        <v>834</v>
-      </c>
-      <c r="D230" t="s">
-        <v>835</v>
-      </c>
-      <c r="E230" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A231" t="s">
-        <v>1072</v>
-      </c>
-      <c r="B231" t="s">
-        <v>819</v>
-      </c>
-      <c r="C231" t="s">
-        <v>835</v>
-      </c>
-      <c r="D231" t="s">
-        <v>836</v>
-      </c>
-      <c r="E231" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A232" t="s">
-        <v>1073</v>
-      </c>
-      <c r="B232" t="s">
-        <v>819</v>
-      </c>
-      <c r="C232" t="s">
-        <v>836</v>
-      </c>
-      <c r="D232" t="s">
-        <v>293</v>
-      </c>
-      <c r="E232" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A233" t="s">
-        <v>1074</v>
-      </c>
-      <c r="B233" t="s">
-        <v>819</v>
-      </c>
-      <c r="C233" t="s">
-        <v>293</v>
-      </c>
-      <c r="D233" t="s">
-        <v>149</v>
-      </c>
-      <c r="E233" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A234" t="s">
-        <v>1075</v>
-      </c>
-      <c r="B234" t="s">
-        <v>819</v>
-      </c>
-      <c r="C234" t="s">
-        <v>149</v>
-      </c>
-      <c r="D234" t="s">
-        <v>837</v>
-      </c>
-      <c r="E234" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A235" t="s">
-        <v>1076</v>
-      </c>
-      <c r="B235" t="s">
-        <v>819</v>
-      </c>
-      <c r="C235" t="s">
-        <v>837</v>
-      </c>
-      <c r="D235" t="s">
-        <v>838</v>
-      </c>
-      <c r="E235" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A236" t="s">
-        <v>1077</v>
-      </c>
-      <c r="B236" t="s">
-        <v>819</v>
-      </c>
-      <c r="C236" t="s">
-        <v>838</v>
-      </c>
-      <c r="D236" t="s">
-        <v>839</v>
-      </c>
-      <c r="E236" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A237" t="s">
-        <v>1078</v>
-      </c>
-      <c r="B237" t="s">
-        <v>819</v>
-      </c>
-      <c r="C237" t="s">
-        <v>839</v>
-      </c>
-      <c r="D237" t="s">
-        <v>58</v>
-      </c>
-      <c r="E237" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A238" t="s">
-        <v>1079</v>
-      </c>
-      <c r="B238" t="s">
-        <v>819</v>
-      </c>
-      <c r="C238" t="s">
-        <v>58</v>
-      </c>
-      <c r="D238" t="s">
-        <v>840</v>
-      </c>
-      <c r="E238" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A239" t="s">
-        <v>1080</v>
-      </c>
-      <c r="B239" t="s">
-        <v>819</v>
-      </c>
-      <c r="C239" t="s">
-        <v>840</v>
-      </c>
-      <c r="D239" t="s">
-        <v>292</v>
-      </c>
-      <c r="E239" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A240" t="s">
-        <v>1081</v>
-      </c>
-      <c r="B240" t="s">
-        <v>819</v>
-      </c>
-      <c r="C240" t="s">
-        <v>292</v>
-      </c>
-      <c r="D240" t="s">
-        <v>71</v>
-      </c>
-      <c r="E240" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A241" t="s">
-        <v>1082</v>
-      </c>
-      <c r="B241" t="s">
-        <v>819</v>
-      </c>
-      <c r="C241" t="s">
-        <v>71</v>
-      </c>
-      <c r="D241" t="s">
-        <v>260</v>
-      </c>
-      <c r="E241" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A242" t="s">
-        <v>1083</v>
-      </c>
-      <c r="B242" t="s">
-        <v>819</v>
-      </c>
-      <c r="C242" t="s">
-        <v>260</v>
-      </c>
-      <c r="D242" t="s">
-        <v>780</v>
-      </c>
-      <c r="E242" t="s">
-        <v>624</v>
+    <row r="547" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A547" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B547" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C547" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D547" t="s">
+        <v>1092</v>
+      </c>
+      <c r="E547" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="548" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A548" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B548" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C548" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D548" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E548" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="549" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A549" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B549" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C549" t="s">
+        <v>1094</v>
+      </c>
+      <c r="D549" t="s">
+        <v>1096</v>
+      </c>
+      <c r="E549" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="550" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A550" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B550" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C550" t="s">
+        <v>1096</v>
+      </c>
+      <c r="D550" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E550" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="551" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A551" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B551" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C551" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D551" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E551" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="552" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A552" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B552" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C552" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D552" t="s">
+        <v>1102</v>
+      </c>
+      <c r="E552" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="553" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A553" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B553" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C553" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D553" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E553" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="554" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A554" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B554" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C554" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D554" t="s">
+        <v>1106</v>
+      </c>
+      <c r="E554" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="555" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A555" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B555" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C555" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D555" t="s">
+        <v>1108</v>
+      </c>
+      <c r="E555" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="556" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A556" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B556" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C556" t="s">
+        <v>1108</v>
+      </c>
+      <c r="D556" t="s">
+        <v>1110</v>
+      </c>
+      <c r="E556" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="557" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A557" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B557" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C557" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D557" t="s">
+        <v>1112</v>
+      </c>
+      <c r="E557" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="558" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A558" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B558" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C558" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D558" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E558" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="559" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A559" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B559" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C559" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D559" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E559" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="560" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A560" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B560" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C560" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D560" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E560" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="561" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A561" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B561" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C561" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D561" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E561" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="562" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A562" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B562" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C562" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D562" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E562" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="563" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A563" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B563" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C563" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D563" t="s">
+        <v>1124</v>
+      </c>
+      <c r="E563" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="564" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A564" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B564" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C564" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D564" t="s">
+        <v>1126</v>
+      </c>
+      <c r="E564" t="s">
+        <v>621</v>
       </c>
     </row>
   </sheetData>
